--- a/inst/extdata/Compendium_meta_data_08-31-2026.xlsx
+++ b/inst/extdata/Compendium_meta_data_08-31-2026.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\priscilla.glenn\Documents\SbCompendium\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\priscilla.glenn\Documents\SbCompendium\inst\extdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B584A984-D6CA-4879-B75F-7185F03C3127}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A835992-634C-4CA6-85A5-24EBA17166CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-14505" yWindow="0" windowWidth="14610" windowHeight="15585" tabRatio="840" activeTab="1" xr2:uid="{63C64222-374D-43E6-8CAD-4EBEFEBA3260}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="840" activeTab="1" xr2:uid="{63C64222-374D-43E6-8CAD-4EBEFEBA3260}"/>
   </bookViews>
   <sheets>
     <sheet name="Exp meta data" sheetId="5" r:id="rId1"/>
@@ -19,7 +19,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Exp meta data'!$A$2:$M$43</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'sample meta data'!$A$1:$K$948</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'sample meta data'!$A$1:$K$947</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -5027,9 +5027,6 @@
     <t>della_LCM_30</t>
   </si>
   <si>
-    <t>NA</t>
-  </si>
-  <si>
     <r>
       <t>Sorghum bicolor Circadian cycling Gene Expression Profiling, BTx623 and 100M</t>
     </r>
@@ -5149,6 +5146,9 @@
   </si>
   <si>
     <t>Sorghum bicolor R07020 CLE treated internodes Gene Expression Profiling</t>
+  </si>
+  <si>
+    <t>In Progress</t>
   </si>
 </sst>
 </file>
@@ -6829,7 +6829,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="29" spans="1:10" ht="17" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A29" s="14" t="s">
         <v>95</v>
       </c>
@@ -6861,12 +6861,12 @@
         <v>92</v>
       </c>
     </row>
-    <row r="30" spans="1:10" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A30" s="40" t="s">
         <v>414</v>
       </c>
       <c r="B30" s="40" t="s">
-        <v>1426</v>
+        <v>1462</v>
       </c>
       <c r="C30" s="34">
         <v>14</v>
@@ -6893,7 +6893,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="31" spans="1:10" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>79</v>
       </c>
@@ -6925,7 +6925,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="32" spans="1:10" s="19" customFormat="1" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:10" s="19" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A32" s="16" t="s">
         <v>74</v>
       </c>
@@ -6960,7 +6960,7 @@
         <v>171</v>
       </c>
       <c r="B33" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
       <c r="C33" s="17">
         <v>11</v>
@@ -6989,7 +6989,7 @@
     </row>
     <row r="34" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
       <c r="B34" t="s">
         <v>1416</v>
@@ -7213,10 +7213,10 @@
     </row>
     <row r="41" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
+        <v>1426</v>
+      </c>
+      <c r="B41" s="33" t="s">
         <v>1427</v>
-      </c>
-      <c r="B41" s="33" t="s">
-        <v>1428</v>
       </c>
       <c r="C41" s="39" t="s">
         <v>1385</v>
@@ -7340,7 +7340,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C79ECD3-055D-4D3A-B8CD-642C5565C2A2}">
-  <dimension ref="A1:K948"/>
+  <dimension ref="A1:K947"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="65.54296875" customWidth="1"/>
@@ -24683,11 +24683,40 @@
       <c r="B603" s="19"/>
     </row>
     <row r="604" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="B604" s="19"/>
+      <c r="A604" t="s">
+        <v>1068</v>
+      </c>
+      <c r="B604" s="19">
+        <v>13</v>
+      </c>
+      <c r="C604" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="D604" s="19" t="s">
+        <v>401</v>
+      </c>
+      <c r="E604" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="F604" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="G604" s="19" t="s">
+        <v>207</v>
+      </c>
+      <c r="I604" s="19" t="s">
+        <v>342</v>
+      </c>
+      <c r="J604" s="19" t="s">
+        <v>383</v>
+      </c>
+      <c r="K604" s="19" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="605" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A605" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="B605" s="19">
         <v>13</v>
@@ -24708,7 +24737,7 @@
         <v>207</v>
       </c>
       <c r="I605" s="19" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="J605" s="19" t="s">
         <v>383</v>
@@ -24719,7 +24748,7 @@
     </row>
     <row r="606" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A606" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="B606" s="19">
         <v>13</v>
@@ -24740,7 +24769,7 @@
         <v>207</v>
       </c>
       <c r="I606" s="19" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="J606" s="19" t="s">
         <v>383</v>
@@ -24751,7 +24780,7 @@
     </row>
     <row r="607" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A607" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="B607" s="19">
         <v>13</v>
@@ -24772,7 +24801,7 @@
         <v>207</v>
       </c>
       <c r="I607" s="19" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="J607" s="19" t="s">
         <v>383</v>
@@ -24783,7 +24812,7 @@
     </row>
     <row r="608" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A608" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="B608" s="19">
         <v>13</v>
@@ -24804,7 +24833,7 @@
         <v>207</v>
       </c>
       <c r="I608" s="19" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="J608" s="19" t="s">
         <v>383</v>
@@ -24815,7 +24844,7 @@
     </row>
     <row r="609" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A609" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="B609" s="19">
         <v>13</v>
@@ -24836,7 +24865,7 @@
         <v>207</v>
       </c>
       <c r="I609" s="19" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="J609" s="19" t="s">
         <v>383</v>
@@ -24847,7 +24876,7 @@
     </row>
     <row r="610" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A610" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="B610" s="19">
         <v>13</v>
@@ -24868,7 +24897,7 @@
         <v>207</v>
       </c>
       <c r="I610" s="19" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="J610" s="19" t="s">
         <v>383</v>
@@ -24879,7 +24908,7 @@
     </row>
     <row r="611" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A611" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="B611" s="19">
         <v>13</v>
@@ -24900,7 +24929,7 @@
         <v>207</v>
       </c>
       <c r="I611" s="19" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="J611" s="19" t="s">
         <v>383</v>
@@ -24911,7 +24940,7 @@
     </row>
     <row r="612" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A612" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="B612" s="19">
         <v>13</v>
@@ -24932,7 +24961,7 @@
         <v>207</v>
       </c>
       <c r="I612" s="19" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="J612" s="19" t="s">
         <v>383</v>
@@ -24943,7 +24972,7 @@
     </row>
     <row r="613" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A613" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="B613" s="19">
         <v>13</v>
@@ -24964,7 +24993,7 @@
         <v>207</v>
       </c>
       <c r="I613" s="19" t="s">
-        <v>350</v>
+        <v>384</v>
       </c>
       <c r="J613" s="19" t="s">
         <v>383</v>
@@ -24975,7 +25004,7 @@
     </row>
     <row r="614" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A614" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="B614" s="19">
         <v>13</v>
@@ -24996,7 +25025,7 @@
         <v>207</v>
       </c>
       <c r="I614" s="19" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="J614" s="19" t="s">
         <v>383</v>
@@ -25007,7 +25036,7 @@
     </row>
     <row r="615" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A615" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="B615" s="19">
         <v>13</v>
@@ -25028,7 +25057,7 @@
         <v>207</v>
       </c>
       <c r="I615" s="19" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="J615" s="19" t="s">
         <v>383</v>
@@ -25039,7 +25068,7 @@
     </row>
     <row r="616" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A616" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="B616" s="19">
         <v>13</v>
@@ -25060,7 +25089,7 @@
         <v>207</v>
       </c>
       <c r="I616" s="19" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="J616" s="19" t="s">
         <v>383</v>
@@ -25071,7 +25100,7 @@
     </row>
     <row r="617" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A617" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="B617" s="19">
         <v>13</v>
@@ -25092,7 +25121,7 @@
         <v>207</v>
       </c>
       <c r="I617" s="19" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="J617" s="19" t="s">
         <v>383</v>
@@ -25103,7 +25132,7 @@
     </row>
     <row r="618" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A618" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="B618" s="19">
         <v>13</v>
@@ -25124,7 +25153,7 @@
         <v>207</v>
       </c>
       <c r="I618" s="19" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="J618" s="19" t="s">
         <v>383</v>
@@ -25135,7 +25164,7 @@
     </row>
     <row r="619" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A619" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="B619" s="19">
         <v>13</v>
@@ -25156,7 +25185,7 @@
         <v>207</v>
       </c>
       <c r="I619" s="19" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="J619" s="19" t="s">
         <v>383</v>
@@ -25167,7 +25196,7 @@
     </row>
     <row r="620" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A620" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="B620" s="19">
         <v>13</v>
@@ -25176,7 +25205,7 @@
         <v>7</v>
       </c>
       <c r="D620" s="19" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="E620" s="19" t="s">
         <v>76</v>
@@ -25188,7 +25217,7 @@
         <v>207</v>
       </c>
       <c r="I620" s="19" t="s">
-        <v>390</v>
+        <v>342</v>
       </c>
       <c r="J620" s="19" t="s">
         <v>383</v>
@@ -25199,7 +25228,7 @@
     </row>
     <row r="621" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A621" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="B621" s="19">
         <v>13</v>
@@ -25220,7 +25249,7 @@
         <v>207</v>
       </c>
       <c r="I621" s="19" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="J621" s="19" t="s">
         <v>383</v>
@@ -25231,7 +25260,7 @@
     </row>
     <row r="622" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A622" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="B622" s="19">
         <v>13</v>
@@ -25252,7 +25281,7 @@
         <v>207</v>
       </c>
       <c r="I622" s="19" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="J622" s="19" t="s">
         <v>383</v>
@@ -25263,7 +25292,7 @@
     </row>
     <row r="623" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A623" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="B623" s="19">
         <v>13</v>
@@ -25284,7 +25313,7 @@
         <v>207</v>
       </c>
       <c r="I623" s="19" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="J623" s="19" t="s">
         <v>383</v>
@@ -25295,7 +25324,7 @@
     </row>
     <row r="624" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A624" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="B624" s="19">
         <v>13</v>
@@ -25316,7 +25345,7 @@
         <v>207</v>
       </c>
       <c r="I624" s="19" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="J624" s="19" t="s">
         <v>383</v>
@@ -25327,7 +25356,7 @@
     </row>
     <row r="625" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A625" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="B625" s="19">
         <v>13</v>
@@ -25348,7 +25377,7 @@
         <v>207</v>
       </c>
       <c r="I625" s="19" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="J625" s="19" t="s">
         <v>383</v>
@@ -25359,7 +25388,7 @@
     </row>
     <row r="626" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A626" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="B626" s="19">
         <v>13</v>
@@ -25380,7 +25409,7 @@
         <v>207</v>
       </c>
       <c r="I626" s="19" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="J626" s="19" t="s">
         <v>383</v>
@@ -25391,7 +25420,7 @@
     </row>
     <row r="627" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A627" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="B627" s="19">
         <v>13</v>
@@ -25412,7 +25441,7 @@
         <v>207</v>
       </c>
       <c r="I627" s="19" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="J627" s="19" t="s">
         <v>383</v>
@@ -25423,7 +25452,7 @@
     </row>
     <row r="628" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A628" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="B628" s="19">
         <v>13</v>
@@ -25444,7 +25473,7 @@
         <v>207</v>
       </c>
       <c r="I628" s="19" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="J628" s="19" t="s">
         <v>383</v>
@@ -25455,7 +25484,7 @@
     </row>
     <row r="629" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A629" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="B629" s="19">
         <v>13</v>
@@ -25476,7 +25505,7 @@
         <v>207</v>
       </c>
       <c r="I629" s="19" t="s">
-        <v>350</v>
+        <v>384</v>
       </c>
       <c r="J629" s="19" t="s">
         <v>383</v>
@@ -25487,7 +25516,7 @@
     </row>
     <row r="630" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A630" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="B630" s="19">
         <v>13</v>
@@ -25508,7 +25537,7 @@
         <v>207</v>
       </c>
       <c r="I630" s="19" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="J630" s="19" t="s">
         <v>383</v>
@@ -25519,7 +25548,7 @@
     </row>
     <row r="631" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A631" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="B631" s="19">
         <v>13</v>
@@ -25540,7 +25569,7 @@
         <v>207</v>
       </c>
       <c r="I631" s="19" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="J631" s="19" t="s">
         <v>383</v>
@@ -25551,7 +25580,7 @@
     </row>
     <row r="632" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A632" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="B632" s="19">
         <v>13</v>
@@ -25572,7 +25601,7 @@
         <v>207</v>
       </c>
       <c r="I632" s="19" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="J632" s="19" t="s">
         <v>383</v>
@@ -25583,7 +25612,7 @@
     </row>
     <row r="633" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A633" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="B633" s="19">
         <v>13</v>
@@ -25604,7 +25633,7 @@
         <v>207</v>
       </c>
       <c r="I633" s="19" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="J633" s="19" t="s">
         <v>383</v>
@@ -25615,7 +25644,7 @@
     </row>
     <row r="634" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A634" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="B634" s="19">
         <v>13</v>
@@ -25636,7 +25665,7 @@
         <v>207</v>
       </c>
       <c r="I634" s="19" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="J634" s="19" t="s">
         <v>383</v>
@@ -25647,7 +25676,7 @@
     </row>
     <row r="635" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A635" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="B635" s="19">
         <v>13</v>
@@ -25668,7 +25697,7 @@
         <v>207</v>
       </c>
       <c r="I635" s="19" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="J635" s="19" t="s">
         <v>383</v>
@@ -25678,43 +25707,43 @@
       </c>
     </row>
     <row r="636" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A636" t="s">
-        <v>1099</v>
-      </c>
-      <c r="B636" s="19">
-        <v>13</v>
-      </c>
-      <c r="C636" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="D636" s="19" t="s">
-        <v>402</v>
-      </c>
-      <c r="E636" s="19" t="s">
-        <v>76</v>
-      </c>
-      <c r="F636" s="19" t="s">
-        <v>80</v>
-      </c>
-      <c r="G636" s="19" t="s">
+      <c r="B636" s="19"/>
+    </row>
+    <row r="637" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A637" t="s">
+        <v>1100</v>
+      </c>
+      <c r="B637" s="19">
+        <v>12</v>
+      </c>
+      <c r="C637" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="D637" s="19" t="s">
+        <v>401</v>
+      </c>
+      <c r="E637" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="F637" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="G637" s="19" t="s">
         <v>207</v>
       </c>
-      <c r="I636" s="19" t="s">
-        <v>390</v>
-      </c>
-      <c r="J636" s="19" t="s">
+      <c r="I637" s="19" t="s">
+        <v>342</v>
+      </c>
+      <c r="J637" s="19" t="s">
         <v>383</v>
       </c>
-      <c r="K636" s="19" t="s">
+      <c r="K637" s="19" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="637" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="B637" s="19"/>
     </row>
     <row r="638" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A638" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="B638" s="19">
         <v>12</v>
@@ -25735,7 +25764,7 @@
         <v>207</v>
       </c>
       <c r="I638" s="19" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="J638" s="19" t="s">
         <v>383</v>
@@ -25746,7 +25775,7 @@
     </row>
     <row r="639" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A639" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="B639" s="19">
         <v>12</v>
@@ -25767,7 +25796,7 @@
         <v>207</v>
       </c>
       <c r="I639" s="19" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="J639" s="19" t="s">
         <v>383</v>
@@ -25778,7 +25807,7 @@
     </row>
     <row r="640" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A640" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="B640" s="19">
         <v>12</v>
@@ -25799,7 +25828,7 @@
         <v>207</v>
       </c>
       <c r="I640" s="19" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="J640" s="19" t="s">
         <v>383</v>
@@ -25810,7 +25839,7 @@
     </row>
     <row r="641" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A641" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="B641" s="19">
         <v>12</v>
@@ -25831,7 +25860,7 @@
         <v>207</v>
       </c>
       <c r="I641" s="19" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="J641" s="19" t="s">
         <v>383</v>
@@ -25842,7 +25871,7 @@
     </row>
     <row r="642" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A642" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="B642" s="19">
         <v>12</v>
@@ -25863,7 +25892,7 @@
         <v>207</v>
       </c>
       <c r="I642" s="19" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="J642" s="19" t="s">
         <v>383</v>
@@ -25874,7 +25903,7 @@
     </row>
     <row r="643" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A643" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="B643" s="19">
         <v>12</v>
@@ -25895,7 +25924,7 @@
         <v>207</v>
       </c>
       <c r="I643" s="19" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="J643" s="19" t="s">
         <v>383</v>
@@ -25906,7 +25935,7 @@
     </row>
     <row r="644" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A644" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="B644" s="19">
         <v>12</v>
@@ -25927,7 +25956,7 @@
         <v>207</v>
       </c>
       <c r="I644" s="19" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="J644" s="19" t="s">
         <v>383</v>
@@ -25938,7 +25967,7 @@
     </row>
     <row r="645" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A645" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="B645" s="19">
         <v>12</v>
@@ -25959,7 +25988,7 @@
         <v>207</v>
       </c>
       <c r="I645" s="19" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="J645" s="19" t="s">
         <v>383</v>
@@ -25970,7 +25999,7 @@
     </row>
     <row r="646" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A646" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="B646" s="19">
         <v>12</v>
@@ -25991,7 +26020,7 @@
         <v>207</v>
       </c>
       <c r="I646" s="19" t="s">
-        <v>350</v>
+        <v>384</v>
       </c>
       <c r="J646" s="19" t="s">
         <v>383</v>
@@ -26002,7 +26031,7 @@
     </row>
     <row r="647" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A647" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="B647" s="19">
         <v>12</v>
@@ -26023,7 +26052,7 @@
         <v>207</v>
       </c>
       <c r="I647" s="19" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="J647" s="19" t="s">
         <v>383</v>
@@ -26034,7 +26063,7 @@
     </row>
     <row r="648" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A648" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="B648" s="19">
         <v>12</v>
@@ -26055,7 +26084,7 @@
         <v>207</v>
       </c>
       <c r="I648" s="19" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="J648" s="19" t="s">
         <v>383</v>
@@ -26066,7 +26095,7 @@
     </row>
     <row r="649" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A649" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="B649" s="19">
         <v>12</v>
@@ -26087,7 +26116,7 @@
         <v>207</v>
       </c>
       <c r="I649" s="19" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="J649" s="19" t="s">
         <v>383</v>
@@ -26098,7 +26127,7 @@
     </row>
     <row r="650" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A650" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="B650" s="19">
         <v>12</v>
@@ -26119,7 +26148,7 @@
         <v>207</v>
       </c>
       <c r="I650" s="19" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="J650" s="19" t="s">
         <v>383</v>
@@ -26130,7 +26159,7 @@
     </row>
     <row r="651" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A651" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="B651" s="19">
         <v>12</v>
@@ -26151,7 +26180,7 @@
         <v>207</v>
       </c>
       <c r="I651" s="19" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="J651" s="19" t="s">
         <v>383</v>
@@ -26162,7 +26191,7 @@
     </row>
     <row r="652" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A652" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="B652" s="19">
         <v>12</v>
@@ -26183,7 +26212,7 @@
         <v>207</v>
       </c>
       <c r="I652" s="19" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="J652" s="19" t="s">
         <v>383</v>
@@ -26194,7 +26223,7 @@
     </row>
     <row r="653" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A653" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="B653" s="19">
         <v>12</v>
@@ -26203,7 +26232,7 @@
         <v>15</v>
       </c>
       <c r="D653" s="19" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="E653" s="19" t="s">
         <v>76</v>
@@ -26215,7 +26244,7 @@
         <v>207</v>
       </c>
       <c r="I653" s="19" t="s">
-        <v>390</v>
+        <v>342</v>
       </c>
       <c r="J653" s="19" t="s">
         <v>383</v>
@@ -26226,7 +26255,7 @@
     </row>
     <row r="654" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A654" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="B654" s="19">
         <v>12</v>
@@ -26247,7 +26276,7 @@
         <v>207</v>
       </c>
       <c r="I654" s="19" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="J654" s="19" t="s">
         <v>383</v>
@@ -26258,7 +26287,7 @@
     </row>
     <row r="655" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A655" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="B655" s="19">
         <v>12</v>
@@ -26279,7 +26308,7 @@
         <v>207</v>
       </c>
       <c r="I655" s="19" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="J655" s="19" t="s">
         <v>383</v>
@@ -26290,7 +26319,7 @@
     </row>
     <row r="656" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A656" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="B656" s="19">
         <v>12</v>
@@ -26311,7 +26340,7 @@
         <v>207</v>
       </c>
       <c r="I656" s="19" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="J656" s="19" t="s">
         <v>383</v>
@@ -26322,7 +26351,7 @@
     </row>
     <row r="657" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A657" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="B657" s="19">
         <v>12</v>
@@ -26343,7 +26372,7 @@
         <v>207</v>
       </c>
       <c r="I657" s="19" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="J657" s="19" t="s">
         <v>383</v>
@@ -26354,7 +26383,7 @@
     </row>
     <row r="658" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A658" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="B658" s="19">
         <v>12</v>
@@ -26375,7 +26404,7 @@
         <v>207</v>
       </c>
       <c r="I658" s="19" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="J658" s="19" t="s">
         <v>383</v>
@@ -26386,7 +26415,7 @@
     </row>
     <row r="659" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A659" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="B659" s="19">
         <v>12</v>
@@ -26407,7 +26436,7 @@
         <v>207</v>
       </c>
       <c r="I659" s="19" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="J659" s="19" t="s">
         <v>383</v>
@@ -26418,7 +26447,7 @@
     </row>
     <row r="660" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A660" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="B660" s="19">
         <v>12</v>
@@ -26439,7 +26468,7 @@
         <v>207</v>
       </c>
       <c r="I660" s="19" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="J660" s="19" t="s">
         <v>383</v>
@@ -26450,7 +26479,7 @@
     </row>
     <row r="661" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A661" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="B661" s="19">
         <v>12</v>
@@ -26471,7 +26500,7 @@
         <v>207</v>
       </c>
       <c r="I661" s="19" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="J661" s="19" t="s">
         <v>383</v>
@@ -26482,7 +26511,7 @@
     </row>
     <row r="662" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A662" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="B662" s="19">
         <v>12</v>
@@ -26503,7 +26532,7 @@
         <v>207</v>
       </c>
       <c r="I662" s="19" t="s">
-        <v>350</v>
+        <v>384</v>
       </c>
       <c r="J662" s="19" t="s">
         <v>383</v>
@@ -26514,7 +26543,7 @@
     </row>
     <row r="663" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A663" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="B663" s="19">
         <v>12</v>
@@ -26535,7 +26564,7 @@
         <v>207</v>
       </c>
       <c r="I663" s="19" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="J663" s="19" t="s">
         <v>383</v>
@@ -26546,7 +26575,7 @@
     </row>
     <row r="664" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A664" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="B664" s="19">
         <v>12</v>
@@ -26567,7 +26596,7 @@
         <v>207</v>
       </c>
       <c r="I664" s="19" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="J664" s="19" t="s">
         <v>383</v>
@@ -26578,7 +26607,7 @@
     </row>
     <row r="665" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A665" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="B665" s="19">
         <v>12</v>
@@ -26599,7 +26628,7 @@
         <v>207</v>
       </c>
       <c r="I665" s="19" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="J665" s="19" t="s">
         <v>383</v>
@@ -26610,7 +26639,7 @@
     </row>
     <row r="666" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A666" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="B666" s="19">
         <v>12</v>
@@ -26631,7 +26660,7 @@
         <v>207</v>
       </c>
       <c r="I666" s="19" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="J666" s="19" t="s">
         <v>383</v>
@@ -26642,7 +26671,7 @@
     </row>
     <row r="667" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A667" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="B667" s="19">
         <v>12</v>
@@ -26663,7 +26692,7 @@
         <v>207</v>
       </c>
       <c r="I667" s="19" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="J667" s="19" t="s">
         <v>383</v>
@@ -26674,7 +26703,7 @@
     </row>
     <row r="668" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A668" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="B668" s="19">
         <v>12</v>
@@ -26695,7 +26724,7 @@
         <v>207</v>
       </c>
       <c r="I668" s="19" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="J668" s="19" t="s">
         <v>383</v>
@@ -26705,43 +26734,40 @@
       </c>
     </row>
     <row r="669" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A669" t="s">
-        <v>1131</v>
-      </c>
-      <c r="B669" s="19">
-        <v>12</v>
-      </c>
-      <c r="C669" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="D669" s="19" t="s">
-        <v>402</v>
-      </c>
-      <c r="E669" s="19" t="s">
-        <v>76</v>
-      </c>
-      <c r="F669" s="19" t="s">
-        <v>80</v>
-      </c>
-      <c r="G669" s="19" t="s">
-        <v>207</v>
-      </c>
-      <c r="I669" s="19" t="s">
-        <v>390</v>
-      </c>
-      <c r="J669" s="19" t="s">
-        <v>383</v>
-      </c>
-      <c r="K669" s="19" t="s">
-        <v>78</v>
-      </c>
+      <c r="B669" s="19"/>
     </row>
     <row r="670" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="B670" s="19"/>
+      <c r="A670" t="s">
+        <v>1132</v>
+      </c>
+      <c r="B670" s="19">
+        <v>11</v>
+      </c>
+      <c r="C670" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="D670" s="19" t="s">
+        <v>85</v>
+      </c>
+      <c r="E670" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="F670" s="19" t="s">
+        <v>91</v>
+      </c>
+      <c r="G670" s="19" t="s">
+        <v>413</v>
+      </c>
+      <c r="H670" s="19" t="s">
+        <v>177</v>
+      </c>
+      <c r="K670" s="19" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="671" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A671" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="B671" s="19">
         <v>11</v>
@@ -26759,10 +26785,10 @@
         <v>91</v>
       </c>
       <c r="G671" s="19" t="s">
-        <v>413</v>
+        <v>292</v>
       </c>
       <c r="H671" s="19" t="s">
-        <v>177</v>
+        <v>198</v>
       </c>
       <c r="K671" s="19" t="s">
         <v>88</v>
@@ -26770,7 +26796,7 @@
     </row>
     <row r="672" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A672" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="B672" s="19">
         <v>11</v>
@@ -26788,10 +26814,10 @@
         <v>91</v>
       </c>
       <c r="G672" s="19" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H672" s="19" t="s">
-        <v>198</v>
+        <v>185</v>
       </c>
       <c r="K672" s="19" t="s">
         <v>88</v>
@@ -26799,7 +26825,7 @@
     </row>
     <row r="673" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A673" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="B673" s="19">
         <v>11</v>
@@ -26817,7 +26843,7 @@
         <v>91</v>
       </c>
       <c r="G673" s="19" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H673" s="19" t="s">
         <v>185</v>
@@ -26828,7 +26854,7 @@
     </row>
     <row r="674" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A674" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="B674" s="19">
         <v>11</v>
@@ -26846,7 +26872,7 @@
         <v>91</v>
       </c>
       <c r="G674" s="19" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H674" s="19" t="s">
         <v>185</v>
@@ -26857,7 +26883,7 @@
     </row>
     <row r="675" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A675" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="B675" s="19">
         <v>11</v>
@@ -26875,7 +26901,7 @@
         <v>91</v>
       </c>
       <c r="G675" s="19" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H675" s="19" t="s">
         <v>185</v>
@@ -26886,7 +26912,7 @@
     </row>
     <row r="676" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A676" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="B676" s="19">
         <v>11</v>
@@ -26904,7 +26930,7 @@
         <v>91</v>
       </c>
       <c r="G676" s="19" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H676" s="19" t="s">
         <v>185</v>
@@ -26915,7 +26941,7 @@
     </row>
     <row r="677" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A677" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="B677" s="19">
         <v>11</v>
@@ -26933,10 +26959,10 @@
         <v>91</v>
       </c>
       <c r="G677" s="19" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H677" s="19" t="s">
-        <v>185</v>
+        <v>202</v>
       </c>
       <c r="K677" s="19" t="s">
         <v>88</v>
@@ -26944,7 +26970,7 @@
     </row>
     <row r="678" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A678" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="B678" s="19">
         <v>11</v>
@@ -26962,7 +26988,7 @@
         <v>91</v>
       </c>
       <c r="G678" s="19" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H678" s="19" t="s">
         <v>202</v>
@@ -26973,7 +26999,7 @@
     </row>
     <row r="679" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A679" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="B679" s="19">
         <v>11</v>
@@ -26991,7 +27017,7 @@
         <v>91</v>
       </c>
       <c r="G679" s="19" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H679" s="19" t="s">
         <v>202</v>
@@ -27002,7 +27028,7 @@
     </row>
     <row r="680" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A680" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="B680" s="19">
         <v>11</v>
@@ -27020,7 +27046,7 @@
         <v>91</v>
       </c>
       <c r="G680" s="19" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H680" s="19" t="s">
         <v>202</v>
@@ -27031,7 +27057,7 @@
     </row>
     <row r="681" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A681" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="B681" s="19">
         <v>11</v>
@@ -27049,7 +27075,7 @@
         <v>91</v>
       </c>
       <c r="G681" s="19" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H681" s="19" t="s">
         <v>202</v>
@@ -27060,7 +27086,7 @@
     </row>
     <row r="682" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A682" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="B682" s="19">
         <v>11</v>
@@ -27078,7 +27104,7 @@
         <v>91</v>
       </c>
       <c r="G682" s="19" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H682" s="19" t="s">
         <v>202</v>
@@ -27089,7 +27115,7 @@
     </row>
     <row r="683" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A683" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="B683" s="19">
         <v>11</v>
@@ -27107,10 +27133,10 @@
         <v>91</v>
       </c>
       <c r="G683" s="19" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H683" s="19" t="s">
-        <v>202</v>
+        <v>179</v>
       </c>
       <c r="K683" s="19" t="s">
         <v>88</v>
@@ -27118,7 +27144,7 @@
     </row>
     <row r="684" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A684" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="B684" s="19">
         <v>11</v>
@@ -27136,7 +27162,7 @@
         <v>91</v>
       </c>
       <c r="G684" s="19" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H684" s="19" t="s">
         <v>179</v>
@@ -27147,7 +27173,7 @@
     </row>
     <row r="685" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A685" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="B685" s="19">
         <v>11</v>
@@ -27165,7 +27191,7 @@
         <v>91</v>
       </c>
       <c r="G685" s="19" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H685" s="19" t="s">
         <v>179</v>
@@ -27176,7 +27202,7 @@
     </row>
     <row r="686" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A686" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="B686" s="19">
         <v>11</v>
@@ -27194,7 +27220,7 @@
         <v>91</v>
       </c>
       <c r="G686" s="19" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H686" s="19" t="s">
         <v>179</v>
@@ -27205,7 +27231,7 @@
     </row>
     <row r="687" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A687" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B687" s="19">
         <v>11</v>
@@ -27223,7 +27249,7 @@
         <v>91</v>
       </c>
       <c r="G687" s="19" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H687" s="19" t="s">
         <v>179</v>
@@ -27234,7 +27260,7 @@
     </row>
     <row r="688" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A688" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="B688" s="19">
         <v>11</v>
@@ -27252,7 +27278,7 @@
         <v>91</v>
       </c>
       <c r="G688" s="19" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H688" s="19" t="s">
         <v>179</v>
@@ -27263,7 +27289,7 @@
     </row>
     <row r="689" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A689" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="B689" s="19">
         <v>11</v>
@@ -27281,10 +27307,10 @@
         <v>91</v>
       </c>
       <c r="G689" s="19" t="s">
-        <v>309</v>
+        <v>1152</v>
       </c>
       <c r="H689" s="19" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="K689" s="19" t="s">
         <v>88</v>
@@ -27292,7 +27318,7 @@
     </row>
     <row r="690" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A690" t="s">
-        <v>1151</v>
+        <v>1153</v>
       </c>
       <c r="B690" s="19">
         <v>11</v>
@@ -27310,7 +27336,7 @@
         <v>91</v>
       </c>
       <c r="G690" s="19" t="s">
-        <v>1152</v>
+        <v>1154</v>
       </c>
       <c r="H690" s="19" t="s">
         <v>185</v>
@@ -27321,7 +27347,7 @@
     </row>
     <row r="691" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A691" t="s">
-        <v>1153</v>
+        <v>1155</v>
       </c>
       <c r="B691" s="19">
         <v>11</v>
@@ -27339,7 +27365,7 @@
         <v>91</v>
       </c>
       <c r="G691" s="19" t="s">
-        <v>1154</v>
+        <v>1156</v>
       </c>
       <c r="H691" s="19" t="s">
         <v>185</v>
@@ -27350,7 +27376,7 @@
     </row>
     <row r="692" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A692" t="s">
-        <v>1155</v>
+        <v>1157</v>
       </c>
       <c r="B692" s="19">
         <v>11</v>
@@ -27368,7 +27394,7 @@
         <v>91</v>
       </c>
       <c r="G692" s="19" t="s">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="H692" s="19" t="s">
         <v>185</v>
@@ -27379,7 +27405,7 @@
     </row>
     <row r="693" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A693" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="B693" s="19">
         <v>11</v>
@@ -27397,7 +27423,7 @@
         <v>91</v>
       </c>
       <c r="G693" s="19" t="s">
-        <v>1158</v>
+        <v>1160</v>
       </c>
       <c r="H693" s="19" t="s">
         <v>185</v>
@@ -27408,7 +27434,7 @@
     </row>
     <row r="694" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A694" t="s">
-        <v>1159</v>
+        <v>1161</v>
       </c>
       <c r="B694" s="19">
         <v>11</v>
@@ -27426,7 +27452,7 @@
         <v>91</v>
       </c>
       <c r="G694" s="19" t="s">
-        <v>1160</v>
+        <v>1162</v>
       </c>
       <c r="H694" s="19" t="s">
         <v>185</v>
@@ -27437,7 +27463,7 @@
     </row>
     <row r="695" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A695" t="s">
-        <v>1161</v>
+        <v>1163</v>
       </c>
       <c r="B695" s="19">
         <v>11</v>
@@ -27455,10 +27481,10 @@
         <v>91</v>
       </c>
       <c r="G695" s="19" t="s">
-        <v>1162</v>
+        <v>1164</v>
       </c>
       <c r="H695" s="19" t="s">
-        <v>185</v>
+        <v>202</v>
       </c>
       <c r="K695" s="19" t="s">
         <v>88</v>
@@ -27466,7 +27492,7 @@
     </row>
     <row r="696" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A696" t="s">
-        <v>1163</v>
+        <v>1165</v>
       </c>
       <c r="B696" s="19">
         <v>11</v>
@@ -27484,7 +27510,7 @@
         <v>91</v>
       </c>
       <c r="G696" s="19" t="s">
-        <v>1164</v>
+        <v>1166</v>
       </c>
       <c r="H696" s="19" t="s">
         <v>202</v>
@@ -27495,7 +27521,7 @@
     </row>
     <row r="697" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A697" t="s">
-        <v>1165</v>
+        <v>1167</v>
       </c>
       <c r="B697" s="19">
         <v>11</v>
@@ -27513,7 +27539,7 @@
         <v>91</v>
       </c>
       <c r="G697" s="19" t="s">
-        <v>1166</v>
+        <v>1168</v>
       </c>
       <c r="H697" s="19" t="s">
         <v>202</v>
@@ -27524,7 +27550,7 @@
     </row>
     <row r="698" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A698" t="s">
-        <v>1167</v>
+        <v>1169</v>
       </c>
       <c r="B698" s="19">
         <v>11</v>
@@ -27542,7 +27568,7 @@
         <v>91</v>
       </c>
       <c r="G698" s="19" t="s">
-        <v>1168</v>
+        <v>1170</v>
       </c>
       <c r="H698" s="19" t="s">
         <v>202</v>
@@ -27553,7 +27579,7 @@
     </row>
     <row r="699" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A699" t="s">
-        <v>1169</v>
+        <v>1171</v>
       </c>
       <c r="B699" s="19">
         <v>11</v>
@@ -27571,7 +27597,7 @@
         <v>91</v>
       </c>
       <c r="G699" s="19" t="s">
-        <v>1170</v>
+        <v>1172</v>
       </c>
       <c r="H699" s="19" t="s">
         <v>202</v>
@@ -27582,7 +27608,7 @@
     </row>
     <row r="700" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A700" t="s">
-        <v>1171</v>
+        <v>1173</v>
       </c>
       <c r="B700" s="19">
         <v>11</v>
@@ -27600,7 +27626,7 @@
         <v>91</v>
       </c>
       <c r="G700" s="19" t="s">
-        <v>1172</v>
+        <v>1174</v>
       </c>
       <c r="H700" s="19" t="s">
         <v>202</v>
@@ -27611,7 +27637,7 @@
     </row>
     <row r="701" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A701" t="s">
-        <v>1173</v>
+        <v>1175</v>
       </c>
       <c r="B701" s="19">
         <v>11</v>
@@ -27629,7 +27655,7 @@
         <v>91</v>
       </c>
       <c r="G701" s="19" t="s">
-        <v>1174</v>
+        <v>1176</v>
       </c>
       <c r="H701" s="19" t="s">
         <v>202</v>
@@ -27640,7 +27666,7 @@
     </row>
     <row r="702" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A702" t="s">
-        <v>1175</v>
+        <v>1177</v>
       </c>
       <c r="B702" s="19">
         <v>11</v>
@@ -27658,7 +27684,7 @@
         <v>91</v>
       </c>
       <c r="G702" s="19" t="s">
-        <v>1176</v>
+        <v>1178</v>
       </c>
       <c r="H702" s="19" t="s">
         <v>202</v>
@@ -27669,7 +27695,7 @@
     </row>
     <row r="703" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A703" t="s">
-        <v>1177</v>
+        <v>1179</v>
       </c>
       <c r="B703" s="19">
         <v>11</v>
@@ -27687,7 +27713,7 @@
         <v>91</v>
       </c>
       <c r="G703" s="19" t="s">
-        <v>1178</v>
+        <v>1180</v>
       </c>
       <c r="H703" s="19" t="s">
         <v>202</v>
@@ -27698,7 +27724,7 @@
     </row>
     <row r="704" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A704" t="s">
-        <v>1179</v>
+        <v>1181</v>
       </c>
       <c r="B704" s="19">
         <v>11</v>
@@ -27716,7 +27742,7 @@
         <v>91</v>
       </c>
       <c r="G704" s="19" t="s">
-        <v>1180</v>
+        <v>1182</v>
       </c>
       <c r="H704" s="19" t="s">
         <v>202</v>
@@ -27727,7 +27753,7 @@
     </row>
     <row r="705" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A705" t="s">
-        <v>1181</v>
+        <v>1183</v>
       </c>
       <c r="B705" s="19">
         <v>11</v>
@@ -27742,13 +27768,13 @@
         <v>76</v>
       </c>
       <c r="F705" s="19" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G705" s="19" t="s">
-        <v>1182</v>
+        <v>207</v>
       </c>
       <c r="H705" s="19" t="s">
-        <v>202</v>
+        <v>177</v>
       </c>
       <c r="K705" s="19" t="s">
         <v>88</v>
@@ -27756,7 +27782,7 @@
     </row>
     <row r="706" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A706" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="B706" s="19">
         <v>11</v>
@@ -27777,7 +27803,7 @@
         <v>207</v>
       </c>
       <c r="H706" s="19" t="s">
-        <v>177</v>
+        <v>198</v>
       </c>
       <c r="K706" s="19" t="s">
         <v>88</v>
@@ -27785,7 +27811,7 @@
     </row>
     <row r="707" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A707" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="B707" s="19">
         <v>11</v>
@@ -27806,7 +27832,7 @@
         <v>207</v>
       </c>
       <c r="H707" s="19" t="s">
-        <v>198</v>
+        <v>185</v>
       </c>
       <c r="K707" s="19" t="s">
         <v>88</v>
@@ -27814,7 +27840,7 @@
     </row>
     <row r="708" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A708" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="B708" s="19">
         <v>11</v>
@@ -27835,7 +27861,7 @@
         <v>207</v>
       </c>
       <c r="H708" s="19" t="s">
-        <v>185</v>
+        <v>202</v>
       </c>
       <c r="K708" s="19" t="s">
         <v>88</v>
@@ -27843,7 +27869,7 @@
     </row>
     <row r="709" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A709" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="B709" s="19">
         <v>11</v>
@@ -27864,7 +27890,7 @@
         <v>207</v>
       </c>
       <c r="H709" s="19" t="s">
-        <v>202</v>
+        <v>179</v>
       </c>
       <c r="K709" s="19" t="s">
         <v>88</v>
@@ -27872,7 +27898,7 @@
     </row>
     <row r="710" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A710" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="B710" s="19">
         <v>11</v>
@@ -27890,10 +27916,10 @@
         <v>80</v>
       </c>
       <c r="G710" s="19" t="s">
-        <v>207</v>
+        <v>266</v>
       </c>
       <c r="H710" s="19" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="K710" s="19" t="s">
         <v>88</v>
@@ -27901,7 +27927,7 @@
     </row>
     <row r="711" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A711" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="B711" s="19">
         <v>11</v>
@@ -27922,7 +27948,7 @@
         <v>266</v>
       </c>
       <c r="H711" s="19" t="s">
-        <v>177</v>
+        <v>198</v>
       </c>
       <c r="K711" s="19" t="s">
         <v>88</v>
@@ -27930,7 +27956,7 @@
     </row>
     <row r="712" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A712" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="B712" s="19">
         <v>11</v>
@@ -27951,7 +27977,7 @@
         <v>266</v>
       </c>
       <c r="H712" s="19" t="s">
-        <v>198</v>
+        <v>185</v>
       </c>
       <c r="K712" s="19" t="s">
         <v>88</v>
@@ -27959,7 +27985,7 @@
     </row>
     <row r="713" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A713" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="B713" s="19">
         <v>11</v>
@@ -27980,7 +28006,7 @@
         <v>266</v>
       </c>
       <c r="H713" s="19" t="s">
-        <v>185</v>
+        <v>202</v>
       </c>
       <c r="K713" s="19" t="s">
         <v>88</v>
@@ -27988,7 +28014,7 @@
     </row>
     <row r="714" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A714" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="B714" s="19">
         <v>11</v>
@@ -28009,47 +28035,53 @@
         <v>266</v>
       </c>
       <c r="H714" s="19" t="s">
-        <v>202</v>
+        <v>179</v>
       </c>
       <c r="K714" s="19" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="715" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A715" t="s">
-        <v>1192</v>
-      </c>
-      <c r="B715" s="19">
-        <v>11</v>
-      </c>
-      <c r="C715" s="19" t="s">
-        <v>5</v>
-      </c>
-      <c r="D715" s="19" t="s">
-        <v>85</v>
-      </c>
-      <c r="E715" s="19" t="s">
-        <v>76</v>
-      </c>
-      <c r="F715" s="19" t="s">
-        <v>80</v>
-      </c>
-      <c r="G715" s="19" t="s">
-        <v>266</v>
-      </c>
-      <c r="H715" s="19" t="s">
-        <v>179</v>
-      </c>
-      <c r="K715" s="19" t="s">
-        <v>88</v>
-      </c>
+      <c r="B715" s="19"/>
     </row>
     <row r="716" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="B716" s="19"/>
+      <c r="A716" t="s">
+        <v>1193</v>
+      </c>
+      <c r="B716" s="19">
+        <v>10</v>
+      </c>
+      <c r="C716" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="D716" s="19" t="s">
+        <v>1194</v>
+      </c>
+      <c r="E716" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="F716" s="19" t="s">
+        <v>91</v>
+      </c>
+      <c r="G716" s="19" t="s">
+        <v>260</v>
+      </c>
+      <c r="H716" s="19" t="s">
+        <v>185</v>
+      </c>
+      <c r="I716" s="19" t="s">
+        <v>186</v>
+      </c>
+      <c r="J716" s="19" t="s">
+        <v>187</v>
+      </c>
+      <c r="K716" s="19" t="s">
+        <v>170</v>
+      </c>
     </row>
     <row r="717" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A717" t="s">
-        <v>1193</v>
+        <v>1195</v>
       </c>
       <c r="B717" s="19">
         <v>10</v>
@@ -28058,7 +28090,7 @@
         <v>3</v>
       </c>
       <c r="D717" s="19" t="s">
-        <v>1194</v>
+        <v>188</v>
       </c>
       <c r="E717" s="19" t="s">
         <v>76</v>
@@ -28082,44 +28114,35 @@
         <v>170</v>
       </c>
     </row>
-    <row r="718" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A718" t="s">
-        <v>1195</v>
-      </c>
-      <c r="B718" s="19">
-        <v>10</v>
-      </c>
-      <c r="C718" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="D718" s="19" t="s">
-        <v>188</v>
-      </c>
-      <c r="E718" s="19" t="s">
-        <v>76</v>
-      </c>
-      <c r="F718" s="19" t="s">
-        <v>91</v>
-      </c>
-      <c r="G718" s="19" t="s">
-        <v>260</v>
-      </c>
-      <c r="H718" s="19" t="s">
-        <v>185</v>
-      </c>
-      <c r="I718" s="19" t="s">
-        <v>186</v>
-      </c>
-      <c r="J718" s="19" t="s">
-        <v>187</v>
-      </c>
-      <c r="K718" s="19" t="s">
-        <v>170</v>
+    <row r="719" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A719" t="s">
+        <v>1196</v>
+      </c>
+      <c r="B719" s="19">
+        <v>9</v>
+      </c>
+      <c r="C719" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="D719" s="19" t="s">
+        <v>315</v>
+      </c>
+      <c r="E719" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="F719" s="19" t="s">
+        <v>91</v>
+      </c>
+      <c r="G719" s="19" t="s">
+        <v>262</v>
+      </c>
+      <c r="K719" s="19" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="720" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A720" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="B720" s="19">
         <v>9</v>
@@ -28128,7 +28151,7 @@
         <v>5</v>
       </c>
       <c r="D720" s="19" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="E720" s="19" t="s">
         <v>76</v>
@@ -28145,7 +28168,7 @@
     </row>
     <row r="721" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A721" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="B721" s="19">
         <v>9</v>
@@ -28154,7 +28177,7 @@
         <v>5</v>
       </c>
       <c r="D721" s="19" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E721" s="19" t="s">
         <v>76</v>
@@ -28163,7 +28186,7 @@
         <v>91</v>
       </c>
       <c r="G721" s="19" t="s">
-        <v>262</v>
+        <v>317</v>
       </c>
       <c r="K721" s="19" t="s">
         <v>92</v>
@@ -28171,7 +28194,7 @@
     </row>
     <row r="722" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A722" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="B722" s="19">
         <v>9</v>
@@ -28180,7 +28203,7 @@
         <v>5</v>
       </c>
       <c r="D722" s="19" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="E722" s="19" t="s">
         <v>76</v>
@@ -28197,7 +28220,7 @@
     </row>
     <row r="723" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A723" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="B723" s="19">
         <v>9</v>
@@ -28215,7 +28238,7 @@
         <v>91</v>
       </c>
       <c r="G723" s="19" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="K723" s="19" t="s">
         <v>92</v>
@@ -28223,7 +28246,7 @@
     </row>
     <row r="724" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A724" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="B724" s="19">
         <v>9</v>
@@ -28241,7 +28264,7 @@
         <v>91</v>
       </c>
       <c r="G724" s="19" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="K724" s="19" t="s">
         <v>92</v>
@@ -28249,7 +28272,7 @@
     </row>
     <row r="725" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A725" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="B725" s="19">
         <v>9</v>
@@ -28267,7 +28290,7 @@
         <v>91</v>
       </c>
       <c r="G725" s="19" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K725" s="19" t="s">
         <v>92</v>
@@ -28275,7 +28298,7 @@
     </row>
     <row r="726" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A726" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="B726" s="19">
         <v>9</v>
@@ -28293,7 +28316,7 @@
         <v>91</v>
       </c>
       <c r="G726" s="19" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="K726" s="19" t="s">
         <v>92</v>
@@ -28301,7 +28324,7 @@
     </row>
     <row r="727" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A727" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="B727" s="19">
         <v>9</v>
@@ -28319,7 +28342,7 @@
         <v>91</v>
       </c>
       <c r="G727" s="19" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="K727" s="19" t="s">
         <v>92</v>
@@ -28327,7 +28350,7 @@
     </row>
     <row r="728" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A728" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="B728" s="19">
         <v>9</v>
@@ -28345,44 +28368,47 @@
         <v>91</v>
       </c>
       <c r="G728" s="19" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="K728" s="19" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="729" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A729" t="s">
-        <v>1205</v>
-      </c>
-      <c r="B729" s="19">
+      <c r="B729" s="19"/>
+    </row>
+    <row r="730" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A730" t="s">
+        <v>1206</v>
+      </c>
+      <c r="B730" s="19">
+        <v>8</v>
+      </c>
+      <c r="C730" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="C729" s="19" t="s">
-        <v>5</v>
-      </c>
-      <c r="D729" s="19" t="s">
-        <v>316</v>
-      </c>
-      <c r="E729" s="19" t="s">
-        <v>76</v>
-      </c>
-      <c r="F729" s="19" t="s">
-        <v>91</v>
-      </c>
-      <c r="G729" s="19" t="s">
-        <v>323</v>
-      </c>
-      <c r="K729" s="19" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="730" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="B730" s="19"/>
+      <c r="D730" s="19" t="s">
+        <v>339</v>
+      </c>
+      <c r="E730" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="F730" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="G730" s="19" t="s">
+        <v>340</v>
+      </c>
+      <c r="J730" s="19" t="s">
+        <v>333</v>
+      </c>
+      <c r="K730" s="19" t="s">
+        <v>108</v>
+      </c>
     </row>
     <row r="731" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A731" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="B731" s="19">
         <v>8</v>
@@ -28403,7 +28429,7 @@
         <v>340</v>
       </c>
       <c r="J731" s="19" t="s">
-        <v>333</v>
+        <v>270</v>
       </c>
       <c r="K731" s="19" t="s">
         <v>108</v>
@@ -28411,7 +28437,7 @@
     </row>
     <row r="732" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A732" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="B732" s="19">
         <v>8</v>
@@ -28432,7 +28458,7 @@
         <v>340</v>
       </c>
       <c r="J732" s="19" t="s">
-        <v>270</v>
+        <v>334</v>
       </c>
       <c r="K732" s="19" t="s">
         <v>108</v>
@@ -28440,7 +28466,7 @@
     </row>
     <row r="733" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A733" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="B733" s="19">
         <v>8</v>
@@ -28461,7 +28487,7 @@
         <v>340</v>
       </c>
       <c r="J733" s="19" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="K733" s="19" t="s">
         <v>108</v>
@@ -28469,7 +28495,7 @@
     </row>
     <row r="734" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A734" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="B734" s="19">
         <v>8</v>
@@ -28490,7 +28516,7 @@
         <v>340</v>
       </c>
       <c r="J734" s="19" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="K734" s="19" t="s">
         <v>108</v>
@@ -28498,7 +28524,7 @@
     </row>
     <row r="735" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A735" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="B735" s="19">
         <v>8</v>
@@ -28519,7 +28545,7 @@
         <v>340</v>
       </c>
       <c r="J735" s="19" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="K735" s="19" t="s">
         <v>108</v>
@@ -28527,7 +28553,7 @@
     </row>
     <row r="736" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A736" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="B736" s="19">
         <v>8</v>
@@ -28548,47 +28574,47 @@
         <v>340</v>
       </c>
       <c r="J736" s="19" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="K736" s="19" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="737" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A737" t="s">
-        <v>1212</v>
-      </c>
-      <c r="B737" s="19">
-        <v>8</v>
-      </c>
-      <c r="C737" s="19" t="s">
+      <c r="B737" s="19"/>
+    </row>
+    <row r="738" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A738" t="s">
+        <v>1358</v>
+      </c>
+      <c r="B738" s="19">
+        <v>7</v>
+      </c>
+      <c r="C738" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="D737" s="19" t="s">
-        <v>339</v>
-      </c>
-      <c r="E737" s="19" t="s">
+      <c r="D738" s="19" t="s">
+        <v>341</v>
+      </c>
+      <c r="E738" s="19" t="s">
         <v>107</v>
       </c>
-      <c r="F737" s="19" t="s">
-        <v>80</v>
-      </c>
-      <c r="G737" s="19" t="s">
-        <v>340</v>
-      </c>
-      <c r="J737" s="19" t="s">
-        <v>338</v>
-      </c>
-      <c r="K737" s="19" t="s">
+      <c r="F738" s="19" t="s">
+        <v>91</v>
+      </c>
+      <c r="G738" s="19" t="s">
+        <v>260</v>
+      </c>
+      <c r="I738" s="19" t="s">
+        <v>342</v>
+      </c>
+      <c r="K738" s="19" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="738" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="B738" s="19"/>
     </row>
     <row r="739" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A739" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="B739" s="19">
         <v>7</v>
@@ -28609,7 +28635,7 @@
         <v>260</v>
       </c>
       <c r="I739" s="19" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="K739" s="19" t="s">
         <v>108</v>
@@ -28617,7 +28643,7 @@
     </row>
     <row r="740" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A740" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
       <c r="B740" s="19">
         <v>7</v>
@@ -28638,7 +28664,7 @@
         <v>260</v>
       </c>
       <c r="I740" s="19" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="K740" s="19" t="s">
         <v>108</v>
@@ -28646,7 +28672,7 @@
     </row>
     <row r="741" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A741" t="s">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="B741" s="19">
         <v>7</v>
@@ -28667,7 +28693,7 @@
         <v>260</v>
       </c>
       <c r="I741" s="19" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="K741" s="19" t="s">
         <v>108</v>
@@ -28675,7 +28701,7 @@
     </row>
     <row r="742" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A742" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="B742" s="19">
         <v>7</v>
@@ -28696,7 +28722,7 @@
         <v>260</v>
       </c>
       <c r="I742" s="19" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K742" s="19" t="s">
         <v>108</v>
@@ -28704,7 +28730,7 @@
     </row>
     <row r="743" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A743" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
       <c r="B743" s="19">
         <v>7</v>
@@ -28725,7 +28751,7 @@
         <v>260</v>
       </c>
       <c r="I743" s="19" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="K743" s="19" t="s">
         <v>108</v>
@@ -28733,7 +28759,7 @@
     </row>
     <row r="744" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A744" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
       <c r="B744" s="19">
         <v>7</v>
@@ -28754,7 +28780,7 @@
         <v>260</v>
       </c>
       <c r="I744" s="19" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="K744" s="19" t="s">
         <v>108</v>
@@ -28762,7 +28788,7 @@
     </row>
     <row r="745" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A745" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="B745" s="19">
         <v>7</v>
@@ -28783,7 +28809,7 @@
         <v>260</v>
       </c>
       <c r="I745" s="19" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="K745" s="19" t="s">
         <v>108</v>
@@ -28791,7 +28817,7 @@
     </row>
     <row r="746" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A746" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="B746" s="19">
         <v>7</v>
@@ -28812,7 +28838,7 @@
         <v>260</v>
       </c>
       <c r="I746" s="19" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K746" s="19" t="s">
         <v>108</v>
@@ -28820,7 +28846,7 @@
     </row>
     <row r="747" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A747" t="s">
-        <v>1366</v>
+        <v>1367</v>
       </c>
       <c r="B747" s="19">
         <v>7</v>
@@ -28829,7 +28855,7 @@
         <v>9</v>
       </c>
       <c r="D747" s="19" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="E747" s="19" t="s">
         <v>107</v>
@@ -28841,7 +28867,7 @@
         <v>260</v>
       </c>
       <c r="I747" s="19" t="s">
-        <v>350</v>
+        <v>342</v>
       </c>
       <c r="K747" s="19" t="s">
         <v>108</v>
@@ -28849,7 +28875,7 @@
     </row>
     <row r="748" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A748" t="s">
-        <v>1367</v>
+        <v>1368</v>
       </c>
       <c r="B748" s="19">
         <v>7</v>
@@ -28870,7 +28896,7 @@
         <v>260</v>
       </c>
       <c r="I748" s="19" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="K748" s="19" t="s">
         <v>108</v>
@@ -28878,7 +28904,7 @@
     </row>
     <row r="749" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A749" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
       <c r="B749" s="19">
         <v>7</v>
@@ -28899,7 +28925,7 @@
         <v>260</v>
       </c>
       <c r="I749" s="19" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="K749" s="19" t="s">
         <v>108</v>
@@ -28907,7 +28933,7 @@
     </row>
     <row r="750" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A750" t="s">
-        <v>1369</v>
+        <v>1370</v>
       </c>
       <c r="B750" s="19">
         <v>7</v>
@@ -28928,7 +28954,7 @@
         <v>260</v>
       </c>
       <c r="I750" s="19" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="K750" s="19" t="s">
         <v>108</v>
@@ -28936,7 +28962,7 @@
     </row>
     <row r="751" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A751" t="s">
-        <v>1370</v>
+        <v>1371</v>
       </c>
       <c r="B751" s="19">
         <v>7</v>
@@ -28957,7 +28983,7 @@
         <v>260</v>
       </c>
       <c r="I751" s="19" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K751" s="19" t="s">
         <v>108</v>
@@ -28965,7 +28991,7 @@
     </row>
     <row r="752" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A752" t="s">
-        <v>1371</v>
+        <v>1372</v>
       </c>
       <c r="B752" s="19">
         <v>7</v>
@@ -28986,7 +29012,7 @@
         <v>260</v>
       </c>
       <c r="I752" s="19" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="K752" s="19" t="s">
         <v>108</v>
@@ -28994,7 +29020,7 @@
     </row>
     <row r="753" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A753" t="s">
-        <v>1372</v>
+        <v>1373</v>
       </c>
       <c r="B753" s="19">
         <v>7</v>
@@ -29015,7 +29041,7 @@
         <v>260</v>
       </c>
       <c r="I753" s="19" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="K753" s="19" t="s">
         <v>108</v>
@@ -29023,7 +29049,7 @@
     </row>
     <row r="754" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A754" t="s">
-        <v>1373</v>
+        <v>1374</v>
       </c>
       <c r="B754" s="19">
         <v>7</v>
@@ -29044,7 +29070,7 @@
         <v>260</v>
       </c>
       <c r="I754" s="19" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="K754" s="19" t="s">
         <v>108</v>
@@ -29052,7 +29078,7 @@
     </row>
     <row r="755" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A755" t="s">
-        <v>1374</v>
+        <v>1375</v>
       </c>
       <c r="B755" s="19">
         <v>7</v>
@@ -29073,7 +29099,7 @@
         <v>260</v>
       </c>
       <c r="I755" s="19" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K755" s="19" t="s">
         <v>108</v>
@@ -29081,19 +29107,19 @@
     </row>
     <row r="756" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A756" t="s">
-        <v>1375</v>
+        <v>1376</v>
       </c>
       <c r="B756" s="19">
         <v>7</v>
       </c>
       <c r="C756" s="19" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D756" s="19" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="E756" s="19" t="s">
-        <v>107</v>
+        <v>76</v>
       </c>
       <c r="F756" s="19" t="s">
         <v>91</v>
@@ -29102,7 +29128,7 @@
         <v>260</v>
       </c>
       <c r="I756" s="19" t="s">
-        <v>350</v>
+        <v>342</v>
       </c>
       <c r="K756" s="19" t="s">
         <v>108</v>
@@ -29110,7 +29136,7 @@
     </row>
     <row r="757" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A757" t="s">
-        <v>1376</v>
+        <v>1377</v>
       </c>
       <c r="B757" s="19">
         <v>7</v>
@@ -29131,7 +29157,7 @@
         <v>260</v>
       </c>
       <c r="I757" s="19" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="K757" s="19" t="s">
         <v>108</v>
@@ -29139,7 +29165,7 @@
     </row>
     <row r="758" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A758" t="s">
-        <v>1377</v>
+        <v>1378</v>
       </c>
       <c r="B758" s="19">
         <v>7</v>
@@ -29160,7 +29186,7 @@
         <v>260</v>
       </c>
       <c r="I758" s="19" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="K758" s="19" t="s">
         <v>108</v>
@@ -29168,7 +29194,7 @@
     </row>
     <row r="759" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A759" t="s">
-        <v>1378</v>
+        <v>1379</v>
       </c>
       <c r="B759" s="19">
         <v>7</v>
@@ -29189,7 +29215,7 @@
         <v>260</v>
       </c>
       <c r="I759" s="19" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="K759" s="19" t="s">
         <v>108</v>
@@ -29197,7 +29223,7 @@
     </row>
     <row r="760" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A760" t="s">
-        <v>1379</v>
+        <v>1380</v>
       </c>
       <c r="B760" s="19">
         <v>7</v>
@@ -29218,7 +29244,7 @@
         <v>260</v>
       </c>
       <c r="I760" s="19" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K760" s="19" t="s">
         <v>108</v>
@@ -29226,7 +29252,7 @@
     </row>
     <row r="761" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A761" t="s">
-        <v>1380</v>
+        <v>1381</v>
       </c>
       <c r="B761" s="19">
         <v>7</v>
@@ -29247,7 +29273,7 @@
         <v>260</v>
       </c>
       <c r="I761" s="19" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="K761" s="19" t="s">
         <v>108</v>
@@ -29255,7 +29281,7 @@
     </row>
     <row r="762" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A762" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
       <c r="B762" s="19">
         <v>7</v>
@@ -29276,7 +29302,7 @@
         <v>260</v>
       </c>
       <c r="I762" s="19" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="K762" s="19" t="s">
         <v>108</v>
@@ -29284,7 +29310,7 @@
     </row>
     <row r="763" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A763" t="s">
-        <v>1382</v>
+        <v>1383</v>
       </c>
       <c r="B763" s="19">
         <v>7</v>
@@ -29305,7 +29331,7 @@
         <v>260</v>
       </c>
       <c r="I763" s="19" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="K763" s="19" t="s">
         <v>108</v>
@@ -29313,7 +29339,7 @@
     </row>
     <row r="764" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A764" t="s">
-        <v>1383</v>
+        <v>1384</v>
       </c>
       <c r="B764" s="19">
         <v>7</v>
@@ -29334,44 +29360,41 @@
         <v>260</v>
       </c>
       <c r="I764" s="19" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K764" s="19" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="765" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A765" t="s">
-        <v>1384</v>
-      </c>
-      <c r="B765" s="19">
-        <v>7</v>
-      </c>
-      <c r="C765" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="D765" s="19" t="s">
-        <v>352</v>
-      </c>
-      <c r="E765" s="19" t="s">
-        <v>76</v>
-      </c>
-      <c r="F765" s="19" t="s">
-        <v>91</v>
-      </c>
-      <c r="G765" s="19" t="s">
-        <v>260</v>
-      </c>
-      <c r="I765" s="19" t="s">
-        <v>350</v>
-      </c>
-      <c r="K765" s="19" t="s">
-        <v>108</v>
+    <row r="766" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A766" t="s">
+        <v>1213</v>
+      </c>
+      <c r="B766" s="19">
+        <v>6</v>
+      </c>
+      <c r="C766" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="D766" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="E766" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="F766" s="19" t="s">
+        <v>91</v>
+      </c>
+      <c r="G766" s="19" t="s">
+        <v>262</v>
+      </c>
+      <c r="K766" s="19" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="767" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A767" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="B767" s="19">
         <v>6</v>
@@ -29389,7 +29412,7 @@
         <v>91</v>
       </c>
       <c r="G767" s="19" t="s">
-        <v>262</v>
+        <v>353</v>
       </c>
       <c r="K767" s="19" t="s">
         <v>92</v>
@@ -29397,7 +29420,7 @@
     </row>
     <row r="768" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A768" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="B768" s="19">
         <v>6</v>
@@ -29415,7 +29438,7 @@
         <v>91</v>
       </c>
       <c r="G768" s="19" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="K768" s="19" t="s">
         <v>92</v>
@@ -29423,7 +29446,7 @@
     </row>
     <row r="769" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A769" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="B769" s="19">
         <v>6</v>
@@ -29441,7 +29464,7 @@
         <v>91</v>
       </c>
       <c r="G769" s="19" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="K769" s="19" t="s">
         <v>92</v>
@@ -29449,7 +29472,7 @@
     </row>
     <row r="770" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A770" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="B770" s="19">
         <v>6</v>
@@ -29467,7 +29490,7 @@
         <v>91</v>
       </c>
       <c r="G770" s="19" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="K770" s="19" t="s">
         <v>92</v>
@@ -29475,7 +29498,7 @@
     </row>
     <row r="771" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A771" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="B771" s="19">
         <v>6</v>
@@ -29493,7 +29516,7 @@
         <v>91</v>
       </c>
       <c r="G771" s="19" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="K771" s="19" t="s">
         <v>92</v>
@@ -29501,7 +29524,7 @@
     </row>
     <row r="772" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A772" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="B772" s="19">
         <v>6</v>
@@ -29519,7 +29542,7 @@
         <v>91</v>
       </c>
       <c r="G772" s="19" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="K772" s="19" t="s">
         <v>92</v>
@@ -29527,16 +29550,16 @@
     </row>
     <row r="773" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A773" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="B773" s="19">
         <v>6</v>
       </c>
       <c r="C773" s="19" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D773" s="19" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="E773" s="19" t="s">
         <v>76</v>
@@ -29545,7 +29568,7 @@
         <v>91</v>
       </c>
       <c r="G773" s="19" t="s">
-        <v>358</v>
+        <v>262</v>
       </c>
       <c r="K773" s="19" t="s">
         <v>92</v>
@@ -29553,7 +29576,7 @@
     </row>
     <row r="774" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A774" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="B774" s="19">
         <v>6</v>
@@ -29571,7 +29594,7 @@
         <v>91</v>
       </c>
       <c r="G774" s="19" t="s">
-        <v>262</v>
+        <v>353</v>
       </c>
       <c r="K774" s="19" t="s">
         <v>92</v>
@@ -29579,7 +29602,7 @@
     </row>
     <row r="775" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A775" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
       <c r="B775" s="19">
         <v>6</v>
@@ -29597,7 +29620,7 @@
         <v>91</v>
       </c>
       <c r="G775" s="19" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="K775" s="19" t="s">
         <v>92</v>
@@ -29605,7 +29628,7 @@
     </row>
     <row r="776" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A776" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="B776" s="19">
         <v>6</v>
@@ -29623,7 +29646,7 @@
         <v>91</v>
       </c>
       <c r="G776" s="19" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="K776" s="19" t="s">
         <v>92</v>
@@ -29631,7 +29654,7 @@
     </row>
     <row r="777" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A777" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="B777" s="19">
         <v>6</v>
@@ -29649,7 +29672,7 @@
         <v>91</v>
       </c>
       <c r="G777" s="19" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="K777" s="19" t="s">
         <v>92</v>
@@ -29657,7 +29680,7 @@
     </row>
     <row r="778" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A778" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="B778" s="19">
         <v>6</v>
@@ -29675,7 +29698,7 @@
         <v>91</v>
       </c>
       <c r="G778" s="19" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="K778" s="19" t="s">
         <v>92</v>
@@ -29683,7 +29706,7 @@
     </row>
     <row r="779" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A779" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="B779" s="19">
         <v>6</v>
@@ -29701,7 +29724,7 @@
         <v>91</v>
       </c>
       <c r="G779" s="19" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="K779" s="19" t="s">
         <v>92</v>
@@ -29709,7 +29732,7 @@
     </row>
     <row r="780" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A780" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="B780" s="19">
         <v>6</v>
@@ -29727,7 +29750,7 @@
         <v>91</v>
       </c>
       <c r="G780" s="19" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="K780" s="19" t="s">
         <v>92</v>
@@ -29735,7 +29758,7 @@
     </row>
     <row r="781" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A781" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="B781" s="19">
         <v>6</v>
@@ -29753,41 +29776,44 @@
         <v>91</v>
       </c>
       <c r="G781" s="19" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="K781" s="19" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="782" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A782" t="s">
-        <v>1228</v>
-      </c>
-      <c r="B782" s="19">
-        <v>6</v>
-      </c>
-      <c r="C782" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="D782" s="19" t="s">
-        <v>94</v>
-      </c>
-      <c r="E782" s="19" t="s">
-        <v>76</v>
-      </c>
-      <c r="F782" s="19" t="s">
-        <v>91</v>
-      </c>
-      <c r="G782" s="19" t="s">
-        <v>358</v>
-      </c>
-      <c r="K782" s="19" t="s">
+    <row r="783" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A783" t="s">
+        <v>1229</v>
+      </c>
+      <c r="B783" s="19">
+        <v>5</v>
+      </c>
+      <c r="C783" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="D783" s="19" t="s">
+        <v>85</v>
+      </c>
+      <c r="E783" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="F783" s="19" t="s">
+        <v>91</v>
+      </c>
+      <c r="G783" s="19" t="s">
+        <v>310</v>
+      </c>
+      <c r="J783" s="19" t="s">
+        <v>311</v>
+      </c>
+      <c r="K783" s="19" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="784" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A784" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="B784" s="19">
         <v>5</v>
@@ -29805,7 +29831,7 @@
         <v>91</v>
       </c>
       <c r="G784" s="19" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="J784" s="19" t="s">
         <v>311</v>
@@ -29816,7 +29842,7 @@
     </row>
     <row r="785" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A785" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="B785" s="19">
         <v>5</v>
@@ -29834,7 +29860,7 @@
         <v>91</v>
       </c>
       <c r="G785" s="19" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="J785" s="19" t="s">
         <v>311</v>
@@ -29845,7 +29871,7 @@
     </row>
     <row r="786" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A786" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="B786" s="19">
         <v>5</v>
@@ -29863,7 +29889,7 @@
         <v>91</v>
       </c>
       <c r="G786" s="19" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="J786" s="19" t="s">
         <v>311</v>
@@ -29873,40 +29899,43 @@
       </c>
     </row>
     <row r="787" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A787" t="s">
-        <v>1232</v>
-      </c>
-      <c r="B787" s="19">
-        <v>5</v>
-      </c>
-      <c r="C787" s="19" t="s">
-        <v>5</v>
-      </c>
-      <c r="D787" s="19" t="s">
-        <v>85</v>
-      </c>
-      <c r="E787" s="19" t="s">
-        <v>76</v>
-      </c>
-      <c r="F787" s="19" t="s">
-        <v>91</v>
-      </c>
-      <c r="G787" s="19" t="s">
-        <v>314</v>
-      </c>
-      <c r="J787" s="19" t="s">
-        <v>311</v>
-      </c>
-      <c r="K787" s="19" t="s">
-        <v>92</v>
-      </c>
+      <c r="B787" s="19"/>
     </row>
     <row r="788" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="B788" s="19"/>
+      <c r="A788" t="s">
+        <v>1233</v>
+      </c>
+      <c r="B788" s="19">
+        <v>4</v>
+      </c>
+      <c r="C788" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="D788" s="19" t="s">
+        <v>382</v>
+      </c>
+      <c r="E788" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="F788" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="G788" s="19" t="s">
+        <v>207</v>
+      </c>
+      <c r="I788" s="19" t="s">
+        <v>342</v>
+      </c>
+      <c r="J788" s="19" t="s">
+        <v>383</v>
+      </c>
+      <c r="K788" s="19" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="789" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A789" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="B789" s="19">
         <v>4</v>
@@ -29927,7 +29956,7 @@
         <v>207</v>
       </c>
       <c r="I789" s="19" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="J789" s="19" t="s">
         <v>383</v>
@@ -29938,7 +29967,7 @@
     </row>
     <row r="790" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A790" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="B790" s="19">
         <v>4</v>
@@ -29959,7 +29988,7 @@
         <v>207</v>
       </c>
       <c r="I790" s="19" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="J790" s="19" t="s">
         <v>383</v>
@@ -29970,7 +29999,7 @@
     </row>
     <row r="791" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A791" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="B791" s="19">
         <v>4</v>
@@ -29991,7 +30020,7 @@
         <v>207</v>
       </c>
       <c r="I791" s="19" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="J791" s="19" t="s">
         <v>383</v>
@@ -30002,7 +30031,7 @@
     </row>
     <row r="792" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A792" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="B792" s="19">
         <v>4</v>
@@ -30023,7 +30052,7 @@
         <v>207</v>
       </c>
       <c r="I792" s="19" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="J792" s="19" t="s">
         <v>383</v>
@@ -30034,7 +30063,7 @@
     </row>
     <row r="793" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A793" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="B793" s="19">
         <v>4</v>
@@ -30055,7 +30084,7 @@
         <v>207</v>
       </c>
       <c r="I793" s="19" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="J793" s="19" t="s">
         <v>383</v>
@@ -30066,7 +30095,7 @@
     </row>
     <row r="794" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A794" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="B794" s="19">
         <v>4</v>
@@ -30087,7 +30116,7 @@
         <v>207</v>
       </c>
       <c r="I794" s="19" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="J794" s="19" t="s">
         <v>383</v>
@@ -30098,7 +30127,7 @@
     </row>
     <row r="795" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A795" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="B795" s="19">
         <v>4</v>
@@ -30119,7 +30148,7 @@
         <v>207</v>
       </c>
       <c r="I795" s="19" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="J795" s="19" t="s">
         <v>383</v>
@@ -30130,7 +30159,7 @@
     </row>
     <row r="796" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A796" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="B796" s="19">
         <v>4</v>
@@ -30151,7 +30180,7 @@
         <v>207</v>
       </c>
       <c r="I796" s="19" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="J796" s="19" t="s">
         <v>383</v>
@@ -30162,7 +30191,7 @@
     </row>
     <row r="797" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A797" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="B797" s="19">
         <v>4</v>
@@ -30183,7 +30212,7 @@
         <v>207</v>
       </c>
       <c r="I797" s="19" t="s">
-        <v>350</v>
+        <v>384</v>
       </c>
       <c r="J797" s="19" t="s">
         <v>383</v>
@@ -30194,7 +30223,7 @@
     </row>
     <row r="798" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A798" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="B798" s="19">
         <v>4</v>
@@ -30215,7 +30244,7 @@
         <v>207</v>
       </c>
       <c r="I798" s="19" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="J798" s="19" t="s">
         <v>383</v>
@@ -30226,7 +30255,7 @@
     </row>
     <row r="799" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A799" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="B799" s="19">
         <v>4</v>
@@ -30247,7 +30276,7 @@
         <v>207</v>
       </c>
       <c r="I799" s="19" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="J799" s="19" t="s">
         <v>383</v>
@@ -30258,7 +30287,7 @@
     </row>
     <row r="800" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A800" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B800" s="19">
         <v>4</v>
@@ -30279,7 +30308,7 @@
         <v>207</v>
       </c>
       <c r="I800" s="19" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="J800" s="19" t="s">
         <v>383</v>
@@ -30290,7 +30319,7 @@
     </row>
     <row r="801" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A801" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="B801" s="19">
         <v>4</v>
@@ -30311,7 +30340,7 @@
         <v>207</v>
       </c>
       <c r="I801" s="19" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="J801" s="19" t="s">
         <v>383</v>
@@ -30322,7 +30351,7 @@
     </row>
     <row r="802" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A802" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="B802" s="19">
         <v>4</v>
@@ -30343,7 +30372,7 @@
         <v>207</v>
       </c>
       <c r="I802" s="19" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="J802" s="19" t="s">
         <v>383</v>
@@ -30354,7 +30383,7 @@
     </row>
     <row r="803" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A803" t="s">
-        <v>1247</v>
+        <v>1248</v>
       </c>
       <c r="B803" s="19">
         <v>4</v>
@@ -30375,7 +30404,7 @@
         <v>207</v>
       </c>
       <c r="I803" s="19" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="J803" s="19" t="s">
         <v>383</v>
@@ -30386,7 +30415,7 @@
     </row>
     <row r="804" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A804" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
       <c r="B804" s="19">
         <v>4</v>
@@ -30395,7 +30424,7 @@
         <v>4</v>
       </c>
       <c r="D804" s="19" t="s">
-        <v>382</v>
+        <v>399</v>
       </c>
       <c r="E804" s="19" t="s">
         <v>81</v>
@@ -30407,7 +30436,7 @@
         <v>207</v>
       </c>
       <c r="I804" s="19" t="s">
-        <v>390</v>
+        <v>342</v>
       </c>
       <c r="J804" s="19" t="s">
         <v>383</v>
@@ -30418,7 +30447,7 @@
     </row>
     <row r="805" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A805" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="B805" s="19">
         <v>4</v>
@@ -30439,7 +30468,7 @@
         <v>207</v>
       </c>
       <c r="I805" s="19" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="J805" s="19" t="s">
         <v>383</v>
@@ -30450,7 +30479,7 @@
     </row>
     <row r="806" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A806" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="B806" s="19">
         <v>4</v>
@@ -30471,7 +30500,7 @@
         <v>207</v>
       </c>
       <c r="I806" s="19" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="J806" s="19" t="s">
         <v>383</v>
@@ -30482,7 +30511,7 @@
     </row>
     <row r="807" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A807" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="B807" s="19">
         <v>4</v>
@@ -30503,7 +30532,7 @@
         <v>207</v>
       </c>
       <c r="I807" s="19" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="J807" s="19" t="s">
         <v>383</v>
@@ -30514,7 +30543,7 @@
     </row>
     <row r="808" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A808" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="B808" s="19">
         <v>4</v>
@@ -30535,7 +30564,7 @@
         <v>207</v>
       </c>
       <c r="I808" s="19" t="s">
-        <v>345</v>
+        <v>400</v>
       </c>
       <c r="J808" s="19" t="s">
         <v>383</v>
@@ -30546,7 +30575,7 @@
     </row>
     <row r="809" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A809" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="B809" s="19">
         <v>4</v>
@@ -30567,7 +30596,7 @@
         <v>207</v>
       </c>
       <c r="I809" s="19" t="s">
-        <v>400</v>
+        <v>347</v>
       </c>
       <c r="J809" s="19" t="s">
         <v>383</v>
@@ -30578,7 +30607,7 @@
     </row>
     <row r="810" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A810" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B810" s="19">
         <v>4</v>
@@ -30599,7 +30628,7 @@
         <v>207</v>
       </c>
       <c r="I810" s="19" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="J810" s="19" t="s">
         <v>383</v>
@@ -30610,7 +30639,7 @@
     </row>
     <row r="811" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A811" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="B811" s="19">
         <v>4</v>
@@ -30631,7 +30660,7 @@
         <v>207</v>
       </c>
       <c r="I811" s="19" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="J811" s="19" t="s">
         <v>383</v>
@@ -30642,7 +30671,7 @@
     </row>
     <row r="812" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A812" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="B812" s="19">
         <v>4</v>
@@ -30663,7 +30692,7 @@
         <v>207</v>
       </c>
       <c r="I812" s="19" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="J812" s="19" t="s">
         <v>383</v>
@@ -30674,7 +30703,7 @@
     </row>
     <row r="813" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A813" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B813" s="19">
         <v>4</v>
@@ -30695,7 +30724,7 @@
         <v>207</v>
       </c>
       <c r="I813" s="19" t="s">
-        <v>350</v>
+        <v>384</v>
       </c>
       <c r="J813" s="19" t="s">
         <v>383</v>
@@ -30706,7 +30735,7 @@
     </row>
     <row r="814" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A814" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="B814" s="19">
         <v>4</v>
@@ -30727,7 +30756,7 @@
         <v>207</v>
       </c>
       <c r="I814" s="19" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="J814" s="19" t="s">
         <v>383</v>
@@ -30738,7 +30767,7 @@
     </row>
     <row r="815" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A815" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="B815" s="19">
         <v>4</v>
@@ -30759,7 +30788,7 @@
         <v>207</v>
       </c>
       <c r="I815" s="19" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="J815" s="19" t="s">
         <v>383</v>
@@ -30770,7 +30799,7 @@
     </row>
     <row r="816" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A816" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="B816" s="19">
         <v>4</v>
@@ -30791,7 +30820,7 @@
         <v>207</v>
       </c>
       <c r="I816" s="19" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="J816" s="19" t="s">
         <v>383</v>
@@ -30802,7 +30831,7 @@
     </row>
     <row r="817" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A817" t="s">
-        <v>1261</v>
+        <v>1262</v>
       </c>
       <c r="B817" s="19">
         <v>4</v>
@@ -30823,7 +30852,7 @@
         <v>207</v>
       </c>
       <c r="I817" s="19" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="J817" s="19" t="s">
         <v>383</v>
@@ -30834,7 +30863,7 @@
     </row>
     <row r="818" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A818" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="B818" s="19">
         <v>4</v>
@@ -30855,7 +30884,7 @@
         <v>207</v>
       </c>
       <c r="I818" s="19" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="J818" s="19" t="s">
         <v>383</v>
@@ -30866,7 +30895,7 @@
     </row>
     <row r="819" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A819" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="B819" s="19">
         <v>4</v>
@@ -30887,7 +30916,7 @@
         <v>207</v>
       </c>
       <c r="I819" s="19" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="J819" s="19" t="s">
         <v>383</v>
@@ -30897,39 +30926,39 @@
       </c>
     </row>
     <row r="820" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A820" t="s">
-        <v>1264</v>
-      </c>
-      <c r="B820" s="19">
-        <v>4</v>
-      </c>
-      <c r="C820" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="D820" s="19" t="s">
-        <v>399</v>
-      </c>
-      <c r="E820" s="19" t="s">
+      <c r="B820" s="19"/>
+    </row>
+    <row r="821" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A821" t="s">
+        <v>1428</v>
+      </c>
+      <c r="B821" s="19">
+        <v>3</v>
+      </c>
+      <c r="C821" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="D821" s="19" t="s">
+        <v>382</v>
+      </c>
+      <c r="E821" s="19" t="s">
         <v>81</v>
       </c>
-      <c r="F820" s="19" t="s">
-        <v>80</v>
-      </c>
-      <c r="G820" s="19" t="s">
+      <c r="F821" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="G821" s="19" t="s">
         <v>207</v>
       </c>
-      <c r="I820" s="19" t="s">
-        <v>390</v>
-      </c>
-      <c r="J820" s="19" t="s">
+      <c r="I821" s="19" t="s">
+        <v>342</v>
+      </c>
+      <c r="J821" s="19" t="s">
         <v>383</v>
       </c>
-      <c r="K820" s="19" t="s">
+      <c r="K821" s="19" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="821" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="B821" s="19"/>
     </row>
     <row r="822" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A822" t="s">
@@ -30954,7 +30983,7 @@
         <v>207</v>
       </c>
       <c r="I822" s="19" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="J822" s="19" t="s">
         <v>383</v>
@@ -30986,7 +31015,7 @@
         <v>207</v>
       </c>
       <c r="I823" s="19" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="J823" s="19" t="s">
         <v>383</v>
@@ -31018,7 +31047,7 @@
         <v>207</v>
       </c>
       <c r="I824" s="19" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="J824" s="19" t="s">
         <v>383</v>
@@ -31050,7 +31079,7 @@
         <v>207</v>
       </c>
       <c r="I825" s="19" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="J825" s="19" t="s">
         <v>383</v>
@@ -31082,7 +31111,7 @@
         <v>207</v>
       </c>
       <c r="I826" s="19" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="J826" s="19" t="s">
         <v>383</v>
@@ -31114,7 +31143,7 @@
         <v>207</v>
       </c>
       <c r="I827" s="19" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="J827" s="19" t="s">
         <v>383</v>
@@ -31146,7 +31175,7 @@
         <v>207</v>
       </c>
       <c r="I828" s="19" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="J828" s="19" t="s">
         <v>383</v>
@@ -31178,7 +31207,7 @@
         <v>207</v>
       </c>
       <c r="I829" s="19" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="J829" s="19" t="s">
         <v>383</v>
@@ -31210,7 +31239,7 @@
         <v>207</v>
       </c>
       <c r="I830" s="19" t="s">
-        <v>350</v>
+        <v>384</v>
       </c>
       <c r="J830" s="19" t="s">
         <v>383</v>
@@ -31242,7 +31271,7 @@
         <v>207</v>
       </c>
       <c r="I831" s="19" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="J831" s="19" t="s">
         <v>383</v>
@@ -31274,7 +31303,7 @@
         <v>207</v>
       </c>
       <c r="I832" s="19" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="J832" s="19" t="s">
         <v>383</v>
@@ -31306,7 +31335,7 @@
         <v>207</v>
       </c>
       <c r="I833" s="19" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="J833" s="19" t="s">
         <v>383</v>
@@ -31338,7 +31367,7 @@
         <v>207</v>
       </c>
       <c r="I834" s="19" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="J834" s="19" t="s">
         <v>383</v>
@@ -31370,7 +31399,7 @@
         <v>207</v>
       </c>
       <c r="I835" s="19" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="J835" s="19" t="s">
         <v>383</v>
@@ -31402,7 +31431,7 @@
         <v>207</v>
       </c>
       <c r="I836" s="19" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="J836" s="19" t="s">
         <v>383</v>
@@ -31422,7 +31451,7 @@
         <v>14</v>
       </c>
       <c r="D837" s="19" t="s">
-        <v>382</v>
+        <v>399</v>
       </c>
       <c r="E837" s="19" t="s">
         <v>81</v>
@@ -31434,7 +31463,7 @@
         <v>207</v>
       </c>
       <c r="I837" s="19" t="s">
-        <v>390</v>
+        <v>342</v>
       </c>
       <c r="J837" s="19" t="s">
         <v>383</v>
@@ -31466,7 +31495,7 @@
         <v>207</v>
       </c>
       <c r="I838" s="19" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="J838" s="19" t="s">
         <v>383</v>
@@ -31498,7 +31527,7 @@
         <v>207</v>
       </c>
       <c r="I839" s="19" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="J839" s="19" t="s">
         <v>383</v>
@@ -31530,7 +31559,7 @@
         <v>207</v>
       </c>
       <c r="I840" s="19" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="J840" s="19" t="s">
         <v>383</v>
@@ -31562,7 +31591,7 @@
         <v>207</v>
       </c>
       <c r="I841" s="19" t="s">
-        <v>345</v>
+        <v>400</v>
       </c>
       <c r="J841" s="19" t="s">
         <v>383</v>
@@ -31594,7 +31623,7 @@
         <v>207</v>
       </c>
       <c r="I842" s="19" t="s">
-        <v>400</v>
+        <v>347</v>
       </c>
       <c r="J842" s="19" t="s">
         <v>383</v>
@@ -31626,7 +31655,7 @@
         <v>207</v>
       </c>
       <c r="I843" s="19" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="J843" s="19" t="s">
         <v>383</v>
@@ -31658,7 +31687,7 @@
         <v>207</v>
       </c>
       <c r="I844" s="19" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="J844" s="19" t="s">
         <v>383</v>
@@ -31690,7 +31719,7 @@
         <v>207</v>
       </c>
       <c r="I845" s="19" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="J845" s="19" t="s">
         <v>383</v>
@@ -31722,7 +31751,7 @@
         <v>207</v>
       </c>
       <c r="I846" s="19" t="s">
-        <v>350</v>
+        <v>384</v>
       </c>
       <c r="J846" s="19" t="s">
         <v>383</v>
@@ -31754,7 +31783,7 @@
         <v>207</v>
       </c>
       <c r="I847" s="19" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="J847" s="19" t="s">
         <v>383</v>
@@ -31786,7 +31815,7 @@
         <v>207</v>
       </c>
       <c r="I848" s="19" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="J848" s="19" t="s">
         <v>383</v>
@@ -31818,7 +31847,7 @@
         <v>207</v>
       </c>
       <c r="I849" s="19" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="J849" s="19" t="s">
         <v>383</v>
@@ -31850,7 +31879,7 @@
         <v>207</v>
       </c>
       <c r="I850" s="19" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="J850" s="19" t="s">
         <v>383</v>
@@ -31882,7 +31911,7 @@
         <v>207</v>
       </c>
       <c r="I851" s="19" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="J851" s="19" t="s">
         <v>383</v>
@@ -31914,7 +31943,7 @@
         <v>207</v>
       </c>
       <c r="I852" s="19" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="J852" s="19" t="s">
         <v>383</v>
@@ -31924,43 +31953,43 @@
       </c>
     </row>
     <row r="853" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A853" t="s">
-        <v>1460</v>
-      </c>
-      <c r="B853" s="19">
+      <c r="B853" s="19"/>
+    </row>
+    <row r="854" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A854" t="s">
+        <v>1265</v>
+      </c>
+      <c r="B854" s="19">
         <v>3</v>
       </c>
-      <c r="C853" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="D853" s="19" t="s">
-        <v>399</v>
-      </c>
-      <c r="E853" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="F853" s="19" t="s">
-        <v>80</v>
-      </c>
-      <c r="G853" s="19" t="s">
+      <c r="C854" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="D854" s="19" t="s">
+        <v>382</v>
+      </c>
+      <c r="E854" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="F854" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="G854" s="19" t="s">
         <v>207</v>
       </c>
-      <c r="I853" s="19" t="s">
-        <v>390</v>
-      </c>
-      <c r="J853" s="19" t="s">
+      <c r="I854" s="19" t="s">
+        <v>342</v>
+      </c>
+      <c r="J854" s="19" t="s">
         <v>383</v>
       </c>
-      <c r="K853" s="19" t="s">
+      <c r="K854" s="19" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="854" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="B854" s="19"/>
     </row>
     <row r="855" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A855" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="B855" s="19">
         <v>3</v>
@@ -31981,7 +32010,7 @@
         <v>207</v>
       </c>
       <c r="I855" s="19" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="J855" s="19" t="s">
         <v>383</v>
@@ -31992,7 +32021,7 @@
     </row>
     <row r="856" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A856" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="B856" s="19">
         <v>3</v>
@@ -32013,7 +32042,7 @@
         <v>207</v>
       </c>
       <c r="I856" s="19" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="J856" s="19" t="s">
         <v>383</v>
@@ -32024,7 +32053,7 @@
     </row>
     <row r="857" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A857" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="B857" s="19">
         <v>3</v>
@@ -32045,7 +32074,7 @@
         <v>207</v>
       </c>
       <c r="I857" s="19" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="J857" s="19" t="s">
         <v>383</v>
@@ -32056,7 +32085,7 @@
     </row>
     <row r="858" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A858" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="B858" s="19">
         <v>3</v>
@@ -32077,7 +32106,7 @@
         <v>207</v>
       </c>
       <c r="I858" s="19" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="J858" s="19" t="s">
         <v>383</v>
@@ -32088,7 +32117,7 @@
     </row>
     <row r="859" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A859" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="B859" s="19">
         <v>3</v>
@@ -32109,7 +32138,7 @@
         <v>207</v>
       </c>
       <c r="I859" s="19" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="J859" s="19" t="s">
         <v>383</v>
@@ -32120,7 +32149,7 @@
     </row>
     <row r="860" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A860" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="B860" s="19">
         <v>3</v>
@@ -32141,7 +32170,7 @@
         <v>207</v>
       </c>
       <c r="I860" s="19" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="J860" s="19" t="s">
         <v>383</v>
@@ -32152,7 +32181,7 @@
     </row>
     <row r="861" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A861" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="B861" s="19">
         <v>3</v>
@@ -32173,7 +32202,7 @@
         <v>207</v>
       </c>
       <c r="I861" s="19" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="J861" s="19" t="s">
         <v>383</v>
@@ -32184,7 +32213,7 @@
     </row>
     <row r="862" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A862" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="B862" s="19">
         <v>3</v>
@@ -32205,7 +32234,7 @@
         <v>207</v>
       </c>
       <c r="I862" s="19" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="J862" s="19" t="s">
         <v>383</v>
@@ -32216,7 +32245,7 @@
     </row>
     <row r="863" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A863" t="s">
-        <v>1273</v>
+        <v>1274</v>
       </c>
       <c r="B863" s="19">
         <v>3</v>
@@ -32237,7 +32266,7 @@
         <v>207</v>
       </c>
       <c r="I863" s="19" t="s">
-        <v>350</v>
+        <v>384</v>
       </c>
       <c r="J863" s="19" t="s">
         <v>383</v>
@@ -32248,7 +32277,7 @@
     </row>
     <row r="864" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A864" t="s">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="B864" s="19">
         <v>3</v>
@@ -32269,7 +32298,7 @@
         <v>207</v>
       </c>
       <c r="I864" s="19" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="J864" s="19" t="s">
         <v>383</v>
@@ -32280,7 +32309,7 @@
     </row>
     <row r="865" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A865" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="B865" s="19">
         <v>3</v>
@@ -32301,7 +32330,7 @@
         <v>207</v>
       </c>
       <c r="I865" s="19" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="J865" s="19" t="s">
         <v>383</v>
@@ -32312,7 +32341,7 @@
     </row>
     <row r="866" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A866" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="B866" s="19">
         <v>3</v>
@@ -32333,7 +32362,7 @@
         <v>207</v>
       </c>
       <c r="I866" s="19" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="J866" s="19" t="s">
         <v>383</v>
@@ -32344,7 +32373,7 @@
     </row>
     <row r="867" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A867" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
       <c r="B867" s="19">
         <v>3</v>
@@ -32365,7 +32394,7 @@
         <v>207</v>
       </c>
       <c r="I867" s="19" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="J867" s="19" t="s">
         <v>383</v>
@@ -32376,7 +32405,7 @@
     </row>
     <row r="868" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A868" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="B868" s="19">
         <v>3</v>
@@ -32397,7 +32426,7 @@
         <v>207</v>
       </c>
       <c r="I868" s="19" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="J868" s="19" t="s">
         <v>383</v>
@@ -32408,7 +32437,7 @@
     </row>
     <row r="869" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A869" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="B869" s="19">
         <v>3</v>
@@ -32429,7 +32458,7 @@
         <v>207</v>
       </c>
       <c r="I869" s="19" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="J869" s="19" t="s">
         <v>383</v>
@@ -32440,7 +32469,7 @@
     </row>
     <row r="870" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A870" t="s">
-        <v>1280</v>
+        <v>1281</v>
       </c>
       <c r="B870" s="19">
         <v>3</v>
@@ -32461,7 +32490,7 @@
         <v>207</v>
       </c>
       <c r="I870" s="19" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="J870" s="19" t="s">
         <v>383</v>
@@ -32472,7 +32501,7 @@
     </row>
     <row r="871" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A871" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="B871" s="19">
         <v>3</v>
@@ -32493,7 +32522,7 @@
         <v>207</v>
       </c>
       <c r="I871" s="19" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="J871" s="19" t="s">
         <v>383</v>
@@ -32504,7 +32533,7 @@
     </row>
     <row r="872" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A872" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="B872" s="19">
         <v>3</v>
@@ -32525,7 +32554,7 @@
         <v>207</v>
       </c>
       <c r="I872" s="19" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="J872" s="19" t="s">
         <v>383</v>
@@ -32536,7 +32565,7 @@
     </row>
     <row r="873" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A873" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
       <c r="B873" s="19">
         <v>3</v>
@@ -32557,7 +32586,7 @@
         <v>207</v>
       </c>
       <c r="I873" s="19" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="J873" s="19" t="s">
         <v>383</v>
@@ -32568,7 +32597,7 @@
     </row>
     <row r="874" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A874" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="B874" s="19">
         <v>3</v>
@@ -32589,7 +32618,7 @@
         <v>207</v>
       </c>
       <c r="I874" s="19" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="J874" s="19" t="s">
         <v>383</v>
@@ -32600,7 +32629,7 @@
     </row>
     <row r="875" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A875" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="B875" s="19">
         <v>3</v>
@@ -32621,7 +32650,7 @@
         <v>207</v>
       </c>
       <c r="I875" s="19" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="J875" s="19" t="s">
         <v>383</v>
@@ -32632,7 +32661,7 @@
     </row>
     <row r="876" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A876" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="B876" s="19">
         <v>3</v>
@@ -32653,7 +32682,7 @@
         <v>207</v>
       </c>
       <c r="I876" s="19" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="J876" s="19" t="s">
         <v>383</v>
@@ -32664,7 +32693,7 @@
     </row>
     <row r="877" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A877" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="B877" s="19">
         <v>3</v>
@@ -32685,7 +32714,7 @@
         <v>207</v>
       </c>
       <c r="I877" s="19" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="J877" s="19" t="s">
         <v>383</v>
@@ -32696,7 +32725,7 @@
     </row>
     <row r="878" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A878" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="B878" s="19">
         <v>3</v>
@@ -32705,10 +32734,10 @@
         <v>7</v>
       </c>
       <c r="D878" s="19" t="s">
-        <v>382</v>
+        <v>399</v>
       </c>
       <c r="E878" s="19" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="F878" s="19" t="s">
         <v>80</v>
@@ -32717,7 +32746,7 @@
         <v>207</v>
       </c>
       <c r="I878" s="19" t="s">
-        <v>398</v>
+        <v>342</v>
       </c>
       <c r="J878" s="19" t="s">
         <v>383</v>
@@ -32728,7 +32757,7 @@
     </row>
     <row r="879" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A879" t="s">
-        <v>1289</v>
+        <v>1290</v>
       </c>
       <c r="B879" s="19">
         <v>3</v>
@@ -32749,7 +32778,7 @@
         <v>207</v>
       </c>
       <c r="I879" s="19" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="J879" s="19" t="s">
         <v>383</v>
@@ -32760,7 +32789,7 @@
     </row>
     <row r="880" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A880" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="B880" s="19">
         <v>3</v>
@@ -32781,7 +32810,7 @@
         <v>207</v>
       </c>
       <c r="I880" s="19" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="J880" s="19" t="s">
         <v>383</v>
@@ -32792,7 +32821,7 @@
     </row>
     <row r="881" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A881" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="B881" s="19">
         <v>3</v>
@@ -32813,7 +32842,7 @@
         <v>207</v>
       </c>
       <c r="I881" s="19" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="J881" s="19" t="s">
         <v>383</v>
@@ -32824,7 +32853,7 @@
     </row>
     <row r="882" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A882" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="B882" s="19">
         <v>3</v>
@@ -32845,7 +32874,7 @@
         <v>207</v>
       </c>
       <c r="I882" s="19" t="s">
-        <v>345</v>
+        <v>400</v>
       </c>
       <c r="J882" s="19" t="s">
         <v>383</v>
@@ -32856,7 +32885,7 @@
     </row>
     <row r="883" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A883" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="B883" s="19">
         <v>3</v>
@@ -32877,7 +32906,7 @@
         <v>207</v>
       </c>
       <c r="I883" s="19" t="s">
-        <v>400</v>
+        <v>347</v>
       </c>
       <c r="J883" s="19" t="s">
         <v>383</v>
@@ -32888,7 +32917,7 @@
     </row>
     <row r="884" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A884" t="s">
-        <v>1294</v>
+        <v>1295</v>
       </c>
       <c r="B884" s="19">
         <v>3</v>
@@ -32909,7 +32938,7 @@
         <v>207</v>
       </c>
       <c r="I884" s="19" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="J884" s="19" t="s">
         <v>383</v>
@@ -32920,7 +32949,7 @@
     </row>
     <row r="885" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A885" t="s">
-        <v>1295</v>
+        <v>1296</v>
       </c>
       <c r="B885" s="19">
         <v>3</v>
@@ -32941,7 +32970,7 @@
         <v>207</v>
       </c>
       <c r="I885" s="19" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="J885" s="19" t="s">
         <v>383</v>
@@ -32952,7 +32981,7 @@
     </row>
     <row r="886" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A886" t="s">
-        <v>1296</v>
+        <v>1297</v>
       </c>
       <c r="B886" s="19">
         <v>3</v>
@@ -32973,7 +33002,7 @@
         <v>207</v>
       </c>
       <c r="I886" s="19" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="J886" s="19" t="s">
         <v>383</v>
@@ -32984,7 +33013,7 @@
     </row>
     <row r="887" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A887" t="s">
-        <v>1297</v>
+        <v>1298</v>
       </c>
       <c r="B887" s="19">
         <v>3</v>
@@ -33005,7 +33034,7 @@
         <v>207</v>
       </c>
       <c r="I887" s="19" t="s">
-        <v>350</v>
+        <v>384</v>
       </c>
       <c r="J887" s="19" t="s">
         <v>383</v>
@@ -33016,7 +33045,7 @@
     </row>
     <row r="888" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A888" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="B888" s="19">
         <v>3</v>
@@ -33037,7 +33066,7 @@
         <v>207</v>
       </c>
       <c r="I888" s="19" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="J888" s="19" t="s">
         <v>383</v>
@@ -33048,7 +33077,7 @@
     </row>
     <row r="889" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A889" t="s">
-        <v>1299</v>
+        <v>1300</v>
       </c>
       <c r="B889" s="19">
         <v>3</v>
@@ -33069,7 +33098,7 @@
         <v>207</v>
       </c>
       <c r="I889" s="19" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="J889" s="19" t="s">
         <v>383</v>
@@ -33080,7 +33109,7 @@
     </row>
     <row r="890" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A890" t="s">
-        <v>1300</v>
+        <v>1301</v>
       </c>
       <c r="B890" s="19">
         <v>3</v>
@@ -33101,7 +33130,7 @@
         <v>207</v>
       </c>
       <c r="I890" s="19" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="J890" s="19" t="s">
         <v>383</v>
@@ -33112,7 +33141,7 @@
     </row>
     <row r="891" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A891" t="s">
-        <v>1301</v>
+        <v>1302</v>
       </c>
       <c r="B891" s="19">
         <v>3</v>
@@ -33133,7 +33162,7 @@
         <v>207</v>
       </c>
       <c r="I891" s="19" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="J891" s="19" t="s">
         <v>383</v>
@@ -33144,7 +33173,7 @@
     </row>
     <row r="892" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A892" t="s">
-        <v>1302</v>
+        <v>1303</v>
       </c>
       <c r="B892" s="19">
         <v>3</v>
@@ -33165,7 +33194,7 @@
         <v>207</v>
       </c>
       <c r="I892" s="19" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="J892" s="19" t="s">
         <v>383</v>
@@ -33176,7 +33205,7 @@
     </row>
     <row r="893" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A893" t="s">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="B893" s="19">
         <v>3</v>
@@ -33197,7 +33226,7 @@
         <v>207</v>
       </c>
       <c r="I893" s="19" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="J893" s="19" t="s">
         <v>383</v>
@@ -33208,7 +33237,7 @@
     </row>
     <row r="894" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A894" t="s">
-        <v>1304</v>
+        <v>1305</v>
       </c>
       <c r="B894" s="19">
         <v>3</v>
@@ -33229,7 +33258,7 @@
         <v>207</v>
       </c>
       <c r="I894" s="19" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="J894" s="19" t="s">
         <v>383</v>
@@ -33240,7 +33269,7 @@
     </row>
     <row r="895" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A895" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="B895" s="19">
         <v>3</v>
@@ -33261,7 +33290,7 @@
         <v>207</v>
       </c>
       <c r="I895" s="19" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="J895" s="19" t="s">
         <v>383</v>
@@ -33272,7 +33301,7 @@
     </row>
     <row r="896" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A896" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="B896" s="19">
         <v>3</v>
@@ -33293,7 +33322,7 @@
         <v>207</v>
       </c>
       <c r="I896" s="19" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="J896" s="19" t="s">
         <v>383</v>
@@ -33304,7 +33333,7 @@
     </row>
     <row r="897" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A897" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="B897" s="19">
         <v>3</v>
@@ -33325,7 +33354,7 @@
         <v>207</v>
       </c>
       <c r="I897" s="19" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="J897" s="19" t="s">
         <v>383</v>
@@ -33336,7 +33365,7 @@
     </row>
     <row r="898" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A898" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="B898" s="19">
         <v>3</v>
@@ -33357,7 +33386,7 @@
         <v>207</v>
       </c>
       <c r="I898" s="19" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="J898" s="19" t="s">
         <v>383</v>
@@ -33368,7 +33397,7 @@
     </row>
     <row r="899" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A899" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="B899" s="19">
         <v>3</v>
@@ -33389,7 +33418,7 @@
         <v>207</v>
       </c>
       <c r="I899" s="19" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="J899" s="19" t="s">
         <v>383</v>
@@ -33400,7 +33429,7 @@
     </row>
     <row r="900" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A900" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="B900" s="19">
         <v>3</v>
@@ -33421,7 +33450,7 @@
         <v>207</v>
       </c>
       <c r="I900" s="19" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="J900" s="19" t="s">
         <v>383</v>
@@ -33432,7 +33461,7 @@
     </row>
     <row r="901" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A901" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="B901" s="19">
         <v>3</v>
@@ -33453,7 +33482,7 @@
         <v>207</v>
       </c>
       <c r="I901" s="19" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="J901" s="19" t="s">
         <v>383</v>
@@ -33463,43 +33492,37 @@
       </c>
     </row>
     <row r="902" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A902" t="s">
-        <v>1312</v>
-      </c>
-      <c r="B902" s="19">
-        <v>3</v>
-      </c>
-      <c r="C902" s="19" t="s">
+      <c r="B902" s="19"/>
+    </row>
+    <row r="903" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A903" t="s">
+        <v>1313</v>
+      </c>
+      <c r="B903" s="19">
+        <v>2</v>
+      </c>
+      <c r="C903" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="D902" s="19" t="s">
-        <v>399</v>
-      </c>
-      <c r="E902" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="F902" s="19" t="s">
-        <v>80</v>
-      </c>
-      <c r="G902" s="19" t="s">
-        <v>207</v>
-      </c>
-      <c r="I902" s="19" t="s">
-        <v>398</v>
-      </c>
-      <c r="J902" s="19" t="s">
-        <v>383</v>
-      </c>
-      <c r="K902" s="19" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="903" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="B903" s="19"/>
+      <c r="D903" s="19" t="s">
+        <v>324</v>
+      </c>
+      <c r="E903" s="19" t="s">
+        <v>120</v>
+      </c>
+      <c r="G903" s="19" t="s">
+        <v>121</v>
+      </c>
+      <c r="J903" s="19" t="s">
+        <v>325</v>
+      </c>
+      <c r="K903" s="19" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="904" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A904" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="B904" s="19">
         <v>2</v>
@@ -33517,7 +33540,7 @@
         <v>121</v>
       </c>
       <c r="J904" s="19" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="K904" s="19" t="s">
         <v>92</v>
@@ -33525,7 +33548,7 @@
     </row>
     <row r="905" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A905" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="B905" s="19">
         <v>2</v>
@@ -33543,7 +33566,7 @@
         <v>121</v>
       </c>
       <c r="J905" s="19" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="K905" s="19" t="s">
         <v>92</v>
@@ -33551,16 +33574,16 @@
     </row>
     <row r="906" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A906" t="s">
-        <v>1315</v>
+        <v>1316</v>
       </c>
       <c r="B906" s="19">
         <v>2</v>
       </c>
       <c r="C906" s="19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D906" s="19" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="E906" s="19" t="s">
         <v>120</v>
@@ -33569,7 +33592,7 @@
         <v>121</v>
       </c>
       <c r="J906" s="19" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="K906" s="19" t="s">
         <v>92</v>
@@ -33577,7 +33600,7 @@
     </row>
     <row r="907" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A907" t="s">
-        <v>1316</v>
+        <v>1317</v>
       </c>
       <c r="B907" s="19">
         <v>2</v>
@@ -33595,7 +33618,7 @@
         <v>121</v>
       </c>
       <c r="J907" s="19" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="K907" s="19" t="s">
         <v>92</v>
@@ -33603,7 +33626,7 @@
     </row>
     <row r="908" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A908" t="s">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="B908" s="19">
         <v>2</v>
@@ -33621,44 +33644,44 @@
         <v>121</v>
       </c>
       <c r="J908" s="19" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="K908" s="19" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="909" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A909" t="s">
-        <v>1318</v>
-      </c>
-      <c r="B909" s="19">
-        <v>2</v>
-      </c>
-      <c r="C909" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="D909" s="19" t="s">
-        <v>328</v>
-      </c>
-      <c r="E909" s="19" t="s">
+      <c r="B909" s="19"/>
+    </row>
+    <row r="910" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A910" t="s">
+        <v>1319</v>
+      </c>
+      <c r="B910" s="19">
+        <v>1</v>
+      </c>
+      <c r="C910" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="D910" s="19" t="s">
+        <v>85</v>
+      </c>
+      <c r="E910" s="19" t="s">
         <v>120</v>
       </c>
-      <c r="G909" s="19" t="s">
-        <v>121</v>
-      </c>
-      <c r="J909" s="19" t="s">
-        <v>327</v>
-      </c>
-      <c r="K909" s="19" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="910" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="B910" s="19"/>
+      <c r="F910" s="19" t="s">
+        <v>91</v>
+      </c>
+      <c r="G910" s="19" t="s">
+        <v>361</v>
+      </c>
+      <c r="K910" s="19" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="911" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A911" t="s">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="B911" s="19">
         <v>1</v>
@@ -33676,7 +33699,7 @@
         <v>91</v>
       </c>
       <c r="G911" s="19" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="K911" s="19" t="s">
         <v>88</v>
@@ -33684,7 +33707,7 @@
     </row>
     <row r="912" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A912" t="s">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="B912" s="19">
         <v>1</v>
@@ -33696,13 +33719,16 @@
         <v>85</v>
       </c>
       <c r="E912" s="19" t="s">
-        <v>120</v>
+        <v>81</v>
       </c>
       <c r="F912" s="19" t="s">
         <v>91</v>
       </c>
       <c r="G912" s="19" t="s">
-        <v>362</v>
+        <v>260</v>
+      </c>
+      <c r="H912" s="19" t="s">
+        <v>363</v>
       </c>
       <c r="K912" s="19" t="s">
         <v>88</v>
@@ -33710,7 +33736,7 @@
     </row>
     <row r="913" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A913" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="B913" s="19">
         <v>1</v>
@@ -33731,7 +33757,7 @@
         <v>260</v>
       </c>
       <c r="H913" s="19" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="K913" s="19" t="s">
         <v>88</v>
@@ -33739,7 +33765,7 @@
     </row>
     <row r="914" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A914" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="B914" s="19">
         <v>1</v>
@@ -33760,7 +33786,7 @@
         <v>260</v>
       </c>
       <c r="H914" s="19" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="K914" s="19" t="s">
         <v>88</v>
@@ -33768,7 +33794,7 @@
     </row>
     <row r="915" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A915" t="s">
-        <v>1323</v>
+        <v>1324</v>
       </c>
       <c r="B915" s="19">
         <v>1</v>
@@ -33780,7 +33806,7 @@
         <v>85</v>
       </c>
       <c r="E915" s="19" t="s">
-        <v>81</v>
+        <v>366</v>
       </c>
       <c r="F915" s="19" t="s">
         <v>91</v>
@@ -33797,7 +33823,7 @@
     </row>
     <row r="916" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A916" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
       <c r="B916" s="19">
         <v>1</v>
@@ -33818,7 +33844,7 @@
         <v>260</v>
       </c>
       <c r="H916" s="19" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="K916" s="19" t="s">
         <v>88</v>
@@ -33826,7 +33852,7 @@
     </row>
     <row r="917" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A917" t="s">
-        <v>1325</v>
+        <v>1326</v>
       </c>
       <c r="B917" s="19">
         <v>1</v>
@@ -33838,7 +33864,7 @@
         <v>85</v>
       </c>
       <c r="E917" s="19" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="F917" s="19" t="s">
         <v>91</v>
@@ -33847,7 +33873,7 @@
         <v>260</v>
       </c>
       <c r="H917" s="19" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="K917" s="19" t="s">
         <v>88</v>
@@ -33855,7 +33881,7 @@
     </row>
     <row r="918" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A918" t="s">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="B918" s="19">
         <v>1</v>
@@ -33876,7 +33902,7 @@
         <v>260</v>
       </c>
       <c r="H918" s="19" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="K918" s="19" t="s">
         <v>88</v>
@@ -33884,7 +33910,7 @@
     </row>
     <row r="919" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A919" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="B919" s="19">
         <v>1</v>
@@ -33896,16 +33922,16 @@
         <v>85</v>
       </c>
       <c r="E919" s="19" t="s">
-        <v>367</v>
+        <v>120</v>
       </c>
       <c r="F919" s="19" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G919" s="19" t="s">
-        <v>260</v>
+        <v>207</v>
       </c>
       <c r="H919" s="19" t="s">
-        <v>368</v>
+        <v>265</v>
       </c>
       <c r="K919" s="19" t="s">
         <v>88</v>
@@ -33913,7 +33939,7 @@
     </row>
     <row r="920" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A920" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="B920" s="19">
         <v>1</v>
@@ -33934,7 +33960,7 @@
         <v>207</v>
       </c>
       <c r="H920" s="19" t="s">
-        <v>265</v>
+        <v>369</v>
       </c>
       <c r="K920" s="19" t="s">
         <v>88</v>
@@ -33942,7 +33968,7 @@
     </row>
     <row r="921" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A921" t="s">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="B921" s="19">
         <v>1</v>
@@ -33963,7 +33989,7 @@
         <v>207</v>
       </c>
       <c r="H921" s="19" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="K921" s="19" t="s">
         <v>88</v>
@@ -33971,7 +33997,7 @@
     </row>
     <row r="922" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A922" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="B922" s="19">
         <v>1</v>
@@ -33983,7 +34009,7 @@
         <v>85</v>
       </c>
       <c r="E922" s="19" t="s">
-        <v>120</v>
+        <v>76</v>
       </c>
       <c r="F922" s="19" t="s">
         <v>80</v>
@@ -33992,7 +34018,7 @@
         <v>207</v>
       </c>
       <c r="H922" s="19" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="K922" s="19" t="s">
         <v>88</v>
@@ -34000,7 +34026,7 @@
     </row>
     <row r="923" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A923" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
       <c r="B923" s="19">
         <v>1</v>
@@ -34021,7 +34047,7 @@
         <v>207</v>
       </c>
       <c r="H923" s="19" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="K923" s="19" t="s">
         <v>88</v>
@@ -34029,7 +34055,7 @@
     </row>
     <row r="924" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A924" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="B924" s="19">
         <v>1</v>
@@ -34050,7 +34076,7 @@
         <v>207</v>
       </c>
       <c r="H924" s="19" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="K924" s="19" t="s">
         <v>88</v>
@@ -34058,7 +34084,7 @@
     </row>
     <row r="925" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A925" t="s">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="B925" s="19">
         <v>1</v>
@@ -34070,7 +34096,7 @@
         <v>85</v>
       </c>
       <c r="E925" s="19" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="F925" s="19" t="s">
         <v>80</v>
@@ -34079,7 +34105,7 @@
         <v>207</v>
       </c>
       <c r="H925" s="19" t="s">
-        <v>373</v>
+        <v>265</v>
       </c>
       <c r="K925" s="19" t="s">
         <v>88</v>
@@ -34087,7 +34113,7 @@
     </row>
     <row r="926" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A926" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="B926" s="19">
         <v>1</v>
@@ -34108,7 +34134,7 @@
         <v>207</v>
       </c>
       <c r="H926" s="19" t="s">
-        <v>265</v>
+        <v>369</v>
       </c>
       <c r="K926" s="19" t="s">
         <v>88</v>
@@ -34116,7 +34142,7 @@
     </row>
     <row r="927" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A927" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
       <c r="B927" s="19">
         <v>1</v>
@@ -34128,7 +34154,7 @@
         <v>85</v>
       </c>
       <c r="E927" s="19" t="s">
-        <v>81</v>
+        <v>366</v>
       </c>
       <c r="F927" s="19" t="s">
         <v>80</v>
@@ -34137,7 +34163,7 @@
         <v>207</v>
       </c>
       <c r="H927" s="19" t="s">
-        <v>369</v>
+        <v>265</v>
       </c>
       <c r="K927" s="19" t="s">
         <v>88</v>
@@ -34145,7 +34171,7 @@
     </row>
     <row r="928" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A928" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
       <c r="B928" s="19">
         <v>1</v>
@@ -34166,7 +34192,7 @@
         <v>207</v>
       </c>
       <c r="H928" s="19" t="s">
-        <v>265</v>
+        <v>369</v>
       </c>
       <c r="K928" s="19" t="s">
         <v>88</v>
@@ -34174,7 +34200,7 @@
     </row>
     <row r="929" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A929" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="B929" s="19">
         <v>1</v>
@@ -34186,7 +34212,7 @@
         <v>85</v>
       </c>
       <c r="E929" s="19" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="F929" s="19" t="s">
         <v>80</v>
@@ -34195,7 +34221,7 @@
         <v>207</v>
       </c>
       <c r="H929" s="19" t="s">
-        <v>369</v>
+        <v>265</v>
       </c>
       <c r="K929" s="19" t="s">
         <v>88</v>
@@ -34203,7 +34229,7 @@
     </row>
     <row r="930" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A930" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="B930" s="19">
         <v>1</v>
@@ -34224,7 +34250,7 @@
         <v>207</v>
       </c>
       <c r="H930" s="19" t="s">
-        <v>265</v>
+        <v>369</v>
       </c>
       <c r="K930" s="19" t="s">
         <v>88</v>
@@ -34232,7 +34258,7 @@
     </row>
     <row r="931" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A931" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="B931" s="19">
         <v>1</v>
@@ -34244,16 +34270,13 @@
         <v>85</v>
       </c>
       <c r="E931" s="19" t="s">
-        <v>367</v>
+        <v>81</v>
       </c>
       <c r="F931" s="19" t="s">
         <v>80</v>
       </c>
       <c r="G931" s="19" t="s">
-        <v>207</v>
-      </c>
-      <c r="H931" s="19" t="s">
-        <v>369</v>
+        <v>193</v>
       </c>
       <c r="K931" s="19" t="s">
         <v>88</v>
@@ -34261,7 +34284,7 @@
     </row>
     <row r="932" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A932" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
       <c r="B932" s="19">
         <v>1</v>
@@ -34273,7 +34296,7 @@
         <v>85</v>
       </c>
       <c r="E932" s="19" t="s">
-        <v>81</v>
+        <v>366</v>
       </c>
       <c r="F932" s="19" t="s">
         <v>80</v>
@@ -34287,7 +34310,7 @@
     </row>
     <row r="933" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A933" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
       <c r="B933" s="19">
         <v>1</v>
@@ -34299,7 +34322,7 @@
         <v>85</v>
       </c>
       <c r="E933" s="19" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="F933" s="19" t="s">
         <v>80</v>
@@ -34313,7 +34336,7 @@
     </row>
     <row r="934" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A934" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
       <c r="B934" s="19">
         <v>1</v>
@@ -34325,13 +34348,13 @@
         <v>85</v>
       </c>
       <c r="E934" s="19" t="s">
-        <v>367</v>
+        <v>81</v>
       </c>
       <c r="F934" s="19" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="G934" s="19" t="s">
-        <v>193</v>
+        <v>374</v>
       </c>
       <c r="K934" s="19" t="s">
         <v>88</v>
@@ -34339,7 +34362,7 @@
     </row>
     <row r="935" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A935" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="B935" s="19">
         <v>1</v>
@@ -34354,10 +34377,7 @@
         <v>81</v>
       </c>
       <c r="F935" s="19" t="s">
-        <v>91</v>
-      </c>
-      <c r="G935" s="19" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="K935" s="19" t="s">
         <v>88</v>
@@ -34365,7 +34385,7 @@
     </row>
     <row r="936" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A936" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="B936" s="19">
         <v>1</v>
@@ -34377,18 +34397,21 @@
         <v>85</v>
       </c>
       <c r="E936" s="19" t="s">
-        <v>81</v>
+        <v>366</v>
       </c>
       <c r="F936" s="19" t="s">
         <v>375</v>
       </c>
+      <c r="G936" s="19" t="s">
+        <v>379</v>
+      </c>
       <c r="K936" s="19" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="937" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A937" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="B937" s="19">
         <v>1</v>
@@ -34406,7 +34429,7 @@
         <v>375</v>
       </c>
       <c r="G937" s="19" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="K937" s="19" t="s">
         <v>88</v>
@@ -34414,7 +34437,7 @@
     </row>
     <row r="938" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A938" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
       <c r="B938" s="19">
         <v>1</v>
@@ -34426,13 +34449,13 @@
         <v>85</v>
       </c>
       <c r="E938" s="19" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="F938" s="19" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="G938" s="19" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="K938" s="19" t="s">
         <v>88</v>
@@ -34440,7 +34463,7 @@
     </row>
     <row r="939" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A939" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
       <c r="B939" s="19">
         <v>1</v>
@@ -34452,13 +34475,13 @@
         <v>85</v>
       </c>
       <c r="E939" s="19" t="s">
-        <v>367</v>
+        <v>1349</v>
       </c>
       <c r="F939" s="19" t="s">
         <v>376</v>
       </c>
       <c r="G939" s="19" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="K939" s="19" t="s">
         <v>88</v>
@@ -34466,7 +34489,7 @@
     </row>
     <row r="940" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A940" t="s">
-        <v>1348</v>
+        <v>1350</v>
       </c>
       <c r="B940" s="19">
         <v>1</v>
@@ -34478,13 +34501,13 @@
         <v>85</v>
       </c>
       <c r="E940" s="19" t="s">
-        <v>1349</v>
+        <v>120</v>
       </c>
       <c r="F940" s="19" t="s">
-        <v>376</v>
+        <v>161</v>
       </c>
       <c r="G940" s="19" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="K940" s="19" t="s">
         <v>88</v>
@@ -34492,7 +34515,7 @@
     </row>
     <row r="941" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A941" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="B941" s="19">
         <v>1</v>
@@ -34510,7 +34533,7 @@
         <v>161</v>
       </c>
       <c r="G941" s="19" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="K941" s="19" t="s">
         <v>88</v>
@@ -34518,7 +34541,7 @@
     </row>
     <row r="942" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A942" t="s">
-        <v>1351</v>
+        <v>1352</v>
       </c>
       <c r="B942" s="19">
         <v>1</v>
@@ -34530,13 +34553,13 @@
         <v>85</v>
       </c>
       <c r="E942" s="19" t="s">
-        <v>120</v>
+        <v>76</v>
       </c>
       <c r="F942" s="19" t="s">
         <v>161</v>
       </c>
       <c r="G942" s="19" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="K942" s="19" t="s">
         <v>88</v>
@@ -34544,7 +34567,7 @@
     </row>
     <row r="943" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A943" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
       <c r="B943" s="19">
         <v>1</v>
@@ -34562,7 +34585,7 @@
         <v>161</v>
       </c>
       <c r="G943" s="19" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="K943" s="19" t="s">
         <v>88</v>
@@ -34570,7 +34593,7 @@
     </row>
     <row r="944" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A944" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B944" s="19">
         <v>1</v>
@@ -34582,13 +34605,13 @@
         <v>85</v>
       </c>
       <c r="E944" s="19" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="F944" s="19" t="s">
         <v>161</v>
       </c>
       <c r="G944" s="19" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="K944" s="19" t="s">
         <v>88</v>
@@ -34596,7 +34619,7 @@
     </row>
     <row r="945" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A945" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
       <c r="B945" s="19">
         <v>1</v>
@@ -34614,7 +34637,7 @@
         <v>161</v>
       </c>
       <c r="G945" s="19" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="K945" s="19" t="s">
         <v>88</v>
@@ -34622,7 +34645,7 @@
     </row>
     <row r="946" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A946" t="s">
-        <v>1355</v>
+        <v>1356</v>
       </c>
       <c r="B946" s="19">
         <v>1</v>
@@ -34634,13 +34657,13 @@
         <v>85</v>
       </c>
       <c r="E946" s="19" t="s">
-        <v>81</v>
+        <v>366</v>
       </c>
       <c r="F946" s="19" t="s">
         <v>161</v>
       </c>
       <c r="G946" s="19" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="K946" s="19" t="s">
         <v>88</v>
@@ -34648,7 +34671,7 @@
     </row>
     <row r="947" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A947" t="s">
-        <v>1356</v>
+        <v>1357</v>
       </c>
       <c r="B947" s="19">
         <v>1</v>
@@ -34660,7 +34683,7 @@
         <v>85</v>
       </c>
       <c r="E947" s="19" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="F947" s="19" t="s">
         <v>161</v>
@@ -34672,37 +34695,11 @@
         <v>88</v>
       </c>
     </row>
-    <row r="948" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A948" t="s">
-        <v>1357</v>
-      </c>
-      <c r="B948" s="19">
-        <v>1</v>
-      </c>
-      <c r="C948" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="D948" s="19" t="s">
-        <v>85</v>
-      </c>
-      <c r="E948" s="19" t="s">
-        <v>367</v>
-      </c>
-      <c r="F948" s="19" t="s">
-        <v>161</v>
-      </c>
-      <c r="G948" s="19" t="s">
-        <v>379</v>
-      </c>
-      <c r="K948" s="19" t="s">
-        <v>88</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:K948" xr:uid="{5C79ECD3-055D-4D3A-B8CD-642C5565C2A2}"/>
+  <autoFilter ref="A1:K947" xr:uid="{5C79ECD3-055D-4D3A-B8CD-642C5565C2A2}"/>
   <phoneticPr fontId="16" type="noConversion"/>
-  <conditionalFormatting sqref="A2:A948">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+  <conditionalFormatting sqref="A2:A947">
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
